--- a/Data_communes/lib_familles_produits.xlsx
+++ b/Data_communes/lib_familles_produits.xlsx
@@ -2786,8 +2786,8 @@
   <dimension ref="A1:F1000"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="4"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" customWidth="1"/>
     <col min="3" max="3" width="56.140625" customWidth="1"/>
     <col min="4" max="4" width="73.7109375" customWidth="1"/>
     <col min="5" max="5" width="35.28515625" customWidth="1"/>

--- a/Data_communes/lib_familles_produits.xlsx
+++ b/Data_communes/lib_familles_produits.xlsx
@@ -4,19 +4,22 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="45" windowWidth="28455" windowHeight="12540"/>
+    <workbookView xWindow="240" yWindow="45" windowWidth="23250" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$G$151</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="687">
   <si>
     <t>code</t>
   </si>
@@ -57,15 +60,9 @@
     <t>PRODUITS ALIMENTAIRES ET BOISSONS NON ALCOOLISEES</t>
   </si>
   <si>
-    <t>Produits alimentaires et boissons non alcoolisees</t>
-  </si>
-  <si>
     <t>PAIN ET CEREALES</t>
   </si>
   <si>
-    <t>Pain et cereales</t>
-  </si>
-  <si>
     <t>VIANDE</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>LAIT, FROMAGE ET OEUFS</t>
   </si>
   <si>
-    <t>Lait, fromage et oeufs</t>
-  </si>
-  <si>
     <t>HUILES ET GRAISSES</t>
   </si>
   <si>
@@ -99,15 +93,9 @@
     <t>LEGUMES</t>
   </si>
   <si>
-    <t>Legumes</t>
-  </si>
-  <si>
     <t>SUCRE, CONFITURE, MIEL, CHOCOLAT ET CONFESERIE</t>
   </si>
   <si>
-    <t>Sucre, confiture, miel, chocolat et confeserie</t>
-  </si>
-  <si>
     <t>PRODUITS ALIMENTAIRES N.C.A.</t>
   </si>
   <si>
@@ -117,33 +105,18 @@
     <t>BOISSONS NON ALCOOLISEES</t>
   </si>
   <si>
-    <t>Boissons non alcoolisees</t>
-  </si>
-  <si>
     <t>CAFE, THE ET CACAO</t>
   </si>
   <si>
-    <t>Cafe, the et cacao</t>
-  </si>
-  <si>
     <t>EAUX MINERALES, BOISSONS RAFRAICHISSANTES, JUS DE FRUITS ET DE LEGUMES (ND)</t>
   </si>
   <si>
-    <t>Eaux minerales, boissons rafraichissantes, jus de fruits et de legumes (nd)</t>
-  </si>
-  <si>
     <t>BOISSONS ALCOOLISEES, TABAC ET STUPEFIANTS</t>
   </si>
   <si>
-    <t>Boissons alcoolisees, tabac et stupefiants</t>
-  </si>
-  <si>
     <t>BOISSONS ALCOOLISEES</t>
   </si>
   <si>
-    <t>Boissons alcoolisees</t>
-  </si>
-  <si>
     <t>SPIRITUEUX</t>
   </si>
   <si>
@@ -153,15 +126,9 @@
     <t>VIN ET BOISSONS FERMENTEES</t>
   </si>
   <si>
-    <t>Vin et boissons fermentees</t>
-  </si>
-  <si>
     <t>BIERE</t>
   </si>
   <si>
-    <t>Biere</t>
-  </si>
-  <si>
     <t>TABAC</t>
   </si>
   <si>
@@ -189,9 +156,6 @@
     <t>VETEMENTS</t>
   </si>
   <si>
-    <t>Vetements</t>
-  </si>
-  <si>
     <t>AUTRES ARTICLES ET ACCESSOIRES D'HABILLEMENT</t>
   </si>
   <si>
@@ -201,9 +165,6 @@
     <t>NETTOYAGE, REPARATION ET LOCATION D'ARTICLES D'HABILLEMENT</t>
   </si>
   <si>
-    <t>Nettoyage, reparation et location d'articles d'habillement</t>
-  </si>
-  <si>
     <t>CHAUSSURES</t>
   </si>
   <si>
@@ -225,9 +186,6 @@
     <t>LOGEMENT, EAU, GAZ, ELECTRICITE ET AUTRES COMBUSTIBLES</t>
   </si>
   <si>
-    <t>Logement, eau, gaz, electricite et autres combustibles</t>
-  </si>
-  <si>
     <t>LOYERS EFFECTIFS</t>
   </si>
   <si>
@@ -237,33 +195,18 @@
     <t>LOYERS EFFECTIVEMENT PAYES PAR LES LOCATAIRES</t>
   </si>
   <si>
-    <t>Loyers effectivement payes par les locataires</t>
-  </si>
-  <si>
     <t>ENTRETIEN ET REPARATION DE LOGEMENT</t>
   </si>
   <si>
-    <t>Entretien et reparation de logement</t>
-  </si>
-  <si>
     <t>FOURNITURES POUR TRAVAUX D'ENTRETIEN ET DE REPARATION DES LOGEMENT</t>
   </si>
   <si>
-    <t>Fournitures pour travaux d'entretien et de reparation des logement</t>
-  </si>
-  <si>
     <t>SERVICES CONCERNANT L'ENTRETIEN ET LES REPARATIONS DU LOGEMENT</t>
   </si>
   <si>
-    <t>Services concernant l'entretien et les reparations du logement</t>
-  </si>
-  <si>
     <t>ALIMENTATION EN EAU ET SERVICES DIVERS LIES AU LOGEMENT</t>
   </si>
   <si>
-    <t>Alimentation en eau et services divers lies au logement</t>
-  </si>
-  <si>
     <t>ALIMENTATION EN EAU ET ASSAINISSEMENT</t>
   </si>
   <si>
@@ -279,15 +222,9 @@
     <t>ELECTRICITE, GAZ ET AUTRES COMBUSTIBLES</t>
   </si>
   <si>
-    <t>Electricite, gaz et autres combustibles</t>
-  </si>
-  <si>
     <t>ELECTRICITE</t>
   </si>
   <si>
-    <t>Electricite</t>
-  </si>
-  <si>
     <t>GAZ</t>
   </si>
   <si>
@@ -303,15 +240,9 @@
     <t>MEUBLES, ARTICLES DE MENAGE ET ENTRETIEN COURANT DU FOYER</t>
   </si>
   <si>
-    <t>Meubles, articles de menage et entretien courant du foyer</t>
-  </si>
-  <si>
     <t>MEUBLES, ARTICLES D'AMEUBLEMENT, TAPIS ET AUTRES REVETEMENTS</t>
   </si>
   <si>
-    <t>Meubles, articles d'ameublement, tapis et autres revetements</t>
-  </si>
-  <si>
     <t>MEUBLES ET ARTICLES D'AMEUBLEMENT</t>
   </si>
   <si>
@@ -321,51 +252,27 @@
     <t>TAPIS ET REVETEMENTS DE SOL DIVERS</t>
   </si>
   <si>
-    <t>Tapis et revetements de sol divers</t>
-  </si>
-  <si>
     <t>ARTICLES DE MENAGE EN TEXTILES</t>
   </si>
   <si>
-    <t>Articles de menage en textiles</t>
-  </si>
-  <si>
     <t>APPAREILS MENAGERS</t>
   </si>
   <si>
-    <t>Appareils menagers</t>
-  </si>
-  <si>
     <t>GROS APPAREILS MENAGERS,ELECTRIQUES OU NON</t>
   </si>
   <si>
-    <t>Gros appareils menagers,electriques ou non</t>
-  </si>
-  <si>
     <t>PETITS APPAREILS ELECTROMENAGERS</t>
   </si>
   <si>
-    <t>Petits appareils electromenagers</t>
-  </si>
-  <si>
     <t>REPARATION D'APPAREILS MENAGERS</t>
   </si>
   <si>
-    <t>Reparation d'appareils menagers</t>
-  </si>
-  <si>
     <t>VERRERIE, VAISSELLE ET USTENSILES DE MENAGE</t>
   </si>
   <si>
-    <t>Verrerie, vaisselle et ustensiles de menage</t>
-  </si>
-  <si>
     <t>OUTILLAGE ET AUTRE MATERIEL POUR LA MAISON ET LE JARDIN</t>
   </si>
   <si>
-    <t>Outillage et autre materiel pour la maison et le jardin</t>
-  </si>
-  <si>
     <t>PETIT OUTILLAGE ET ACCESSOIRES DIVERS</t>
   </si>
   <si>
@@ -375,33 +282,18 @@
     <t>BIENS ET SERVICES LIES A L'ENTRETIEN COURANT DU FOYER</t>
   </si>
   <si>
-    <t>Biens et services lies a l'entretien courant du foyer</t>
-  </si>
-  <si>
     <t>BIENS D'EQUIPEMENT MENAGER NON DURABLES</t>
   </si>
   <si>
-    <t>Biens d'equipement menager non durables</t>
-  </si>
-  <si>
     <t>SERVICES DOMESTIQUES ET SERVICES MENAGERS</t>
   </si>
   <si>
-    <t>Services domestiques et services menagers</t>
-  </si>
-  <si>
     <t>SANTE</t>
   </si>
   <si>
-    <t>Sante</t>
-  </si>
-  <si>
     <t>- Produits, appareils et matériels médicaux</t>
   </si>
   <si>
-    <t>- produits, appareils et matériels médicaux</t>
-  </si>
-  <si>
     <t>PRODUITS PHARMACEUTIQUES</t>
   </si>
   <si>
@@ -411,15 +303,9 @@
     <t>PRODUITS MEDICAUX DIVERS</t>
   </si>
   <si>
-    <t>Produits medicaux divers</t>
-  </si>
-  <si>
     <t>APPAREILS ET MATERIEL THERAPEUTIQUES</t>
   </si>
   <si>
-    <t>Appareils et materiel therapeutiques</t>
-  </si>
-  <si>
     <t>SERVICES AMBULATOIRES</t>
   </si>
   <si>
@@ -429,9 +315,6 @@
     <t>SERVICES MEDICAUX</t>
   </si>
   <si>
-    <t>Services medicaux</t>
-  </si>
-  <si>
     <t>SERVICES DENTAIRES</t>
   </si>
   <si>
@@ -441,9 +324,6 @@
     <t>SERVICES PARAMEDICAUX</t>
   </si>
   <si>
-    <t>Services paramedicaux</t>
-  </si>
-  <si>
     <t>SERVICES HOSPITALIERS</t>
   </si>
   <si>
@@ -459,9 +339,6 @@
     <t>ACHAT DE VEHICULES</t>
   </si>
   <si>
-    <t>Achat de vehicules</t>
-  </si>
-  <si>
     <t>VOITURES AUTOMOBILES</t>
   </si>
   <si>
@@ -483,33 +360,18 @@
     <t>DEPENSES D'UTILISATION DES VEHICULES</t>
   </si>
   <si>
-    <t>Depenses d'utilisation des vehicules</t>
-  </si>
-  <si>
     <t>PIECES DE RECHANGE ET ACCESSOIRES POUR VEHICULES DE TOURISME</t>
   </si>
   <si>
-    <t>Pieces de rechange et accessoires pour vehicules de tourisme</t>
-  </si>
-  <si>
     <t>CARBURANTS ET LUBRIFIANTS POUR VEHICULES DE TOURISME</t>
   </si>
   <si>
-    <t>Carburants et lubrifiants pour vehicules de tourisme</t>
-  </si>
-  <si>
     <t>ENTRETIEN ET REPARATION DE VEHICULES PARTICULIERS</t>
   </si>
   <si>
-    <t>Entretien et reparation de vehicules particuliers</t>
-  </si>
-  <si>
     <t>SERVICES DIVERS LIES AUX VEHICULES PARTICULIERS</t>
   </si>
   <si>
-    <t>Services divers lies aux vehicules particuliers</t>
-  </si>
-  <si>
     <t>SERVICES DE TRANSPORT</t>
   </si>
   <si>
@@ -531,9 +393,6 @@
     <t>TRANSPORT AERIEN DE PASSAGERS</t>
   </si>
   <si>
-    <t>Transport aerien de passagers</t>
-  </si>
-  <si>
     <t>COMMUNICATIONS</t>
   </si>
   <si>
@@ -549,15 +408,9 @@
     <t>MATERIEL DE TELEPHONIE ET DE TELECOPIE</t>
   </si>
   <si>
-    <t>Materiel de telephonie et de telecopie</t>
-  </si>
-  <si>
     <t>SERVICES DE TELEPHONIE ET DE TELECOPIE</t>
   </si>
   <si>
-    <t>Services de telephonie et de telecopie</t>
-  </si>
-  <si>
     <t>LOISIRS ET CULTURE</t>
   </si>
   <si>
@@ -585,9 +438,6 @@
     <t>MATERIEL DE TRAITEMENT DE L'INFORMATION</t>
   </si>
   <si>
-    <t>Materiel de traitement de l'information</t>
-  </si>
-  <si>
     <t>SUPPORTS D'ENREGISTREMENT</t>
   </si>
   <si>
@@ -609,9 +459,6 @@
     <t>AUTRES ARTICLES ET MATERIEL DE LOISIRS, DE JARDINAGE ET ANIM</t>
   </si>
   <si>
-    <t>Autres articles et materiel de loisirs, de jardinage et anim</t>
-  </si>
-  <si>
     <t>JEUX, JOUETS ET PASSE-TEMPS</t>
   </si>
   <si>
@@ -633,15 +480,9 @@
     <t>SERVICES RECREATIFS ET CULTURELS</t>
   </si>
   <si>
-    <t>Services recreatifs et culturels</t>
-  </si>
-  <si>
     <t>SERVICES RCREATIFS ET SPORTIFS</t>
   </si>
   <si>
-    <t>Services rcreatifs et sportifs</t>
-  </si>
-  <si>
     <t>SERVICES CULTURELS</t>
   </si>
   <si>
@@ -669,15 +510,9 @@
     <t>JOURNAUX ET PUBLICATIONS PERIODIQUES</t>
   </si>
   <si>
-    <t>Journaux et publications periodiques</t>
-  </si>
-  <si>
     <t>PAPETERIE ET MATERIEL DE DESSIN</t>
   </si>
   <si>
-    <t>Papeterie et materiel de dessin</t>
-  </si>
-  <si>
     <t>FORFAITS TOURISTIQUES</t>
   </si>
   <si>
@@ -693,9 +528,6 @@
     <t>ENSEIGNEMENT PREELEMENTAIRE ET PRIMAIRE</t>
   </si>
   <si>
-    <t>Enseignement preelementaire et primaire</t>
-  </si>
-  <si>
     <t>ENSEIGNEMENT SECONDAIRE</t>
   </si>
   <si>
@@ -705,27 +537,15 @@
     <t>ENSEIGNEMENT POSTSECONDAIRE NON SUPERIEUR</t>
   </si>
   <si>
-    <t>Enseignement postsecondaire non superieur</t>
-  </si>
-  <si>
     <t>ENSEIGNEMENT SUPERIEUR</t>
   </si>
   <si>
-    <t>Enseignement superieur</t>
-  </si>
-  <si>
     <t>ENSEIGNEMENT NON DEFINI PAR NIVEAU</t>
   </si>
   <si>
-    <t>Enseignement non defini par niveau</t>
-  </si>
-  <si>
     <t>RESTAURANTS ET HOTELS</t>
   </si>
   <si>
-    <t>Restaurants et hotels</t>
-  </si>
-  <si>
     <t>SERVICES DE RESTAURATION</t>
   </si>
   <si>
@@ -735,9 +555,6 @@
     <t>RESTAURANTS, CAFES ET ETABLISSEMENTS SIMILAIRES</t>
   </si>
   <si>
-    <t>Restaurants, cafes et etablissements similaires</t>
-  </si>
-  <si>
     <t>CANTINES</t>
   </si>
   <si>
@@ -747,9 +564,6 @@
     <t>SERVICES D'HEBERGEMENT</t>
   </si>
   <si>
-    <t>Services d'hebergement</t>
-  </si>
-  <si>
     <t>BIENS ET SERVICES DIVERS</t>
   </si>
   <si>
@@ -765,15 +579,9 @@
     <t>SALONS DE COIFFURE ET INSTITUTS DE SOINS ET DE BEAUTE</t>
   </si>
   <si>
-    <t>Salons de coiffure et instituts de soins et de beaute</t>
-  </si>
-  <si>
     <t>APPAREILS ELECTRIQUES POUR SOINS CORPORELS</t>
   </si>
   <si>
-    <t>Appareils electriques pour soins corporels</t>
-  </si>
-  <si>
     <t>AUTRES APPAREILS, ARTICLES ET PRODUITS POUR SOINS CORPORELS</t>
   </si>
   <si>
@@ -819,9 +627,6 @@
     <t>COUT DES SERVICES D'INTERMEDIATION FINANCIER</t>
   </si>
   <si>
-    <t>Cout des services d'intermediation financier</t>
-  </si>
-  <si>
     <t>AUTRES SERVICES</t>
   </si>
   <si>
@@ -837,330 +642,6 @@
     <t>ang</t>
   </si>
   <si>
-    <t>'0111</t>
-  </si>
-  <si>
-    <t>'022</t>
-  </si>
-  <si>
-    <t>'031</t>
-  </si>
-  <si>
-    <t>'0311</t>
-  </si>
-  <si>
-    <t>'0312</t>
-  </si>
-  <si>
-    <t>'0313</t>
-  </si>
-  <si>
-    <t>'0314</t>
-  </si>
-  <si>
-    <t>'032</t>
-  </si>
-  <si>
-    <t>'0321</t>
-  </si>
-  <si>
-    <t>'0322</t>
-  </si>
-  <si>
-    <t>'041</t>
-  </si>
-  <si>
-    <t>'0411</t>
-  </si>
-  <si>
-    <t>'043</t>
-  </si>
-  <si>
-    <t>'0431</t>
-  </si>
-  <si>
-    <t>'0432</t>
-  </si>
-  <si>
-    <t>'044</t>
-  </si>
-  <si>
-    <t>'0441</t>
-  </si>
-  <si>
-    <t>'0442</t>
-  </si>
-  <si>
-    <t>'0444</t>
-  </si>
-  <si>
-    <t>'045</t>
-  </si>
-  <si>
-    <t>'0451</t>
-  </si>
-  <si>
-    <t>'0452</t>
-  </si>
-  <si>
-    <t>'0454</t>
-  </si>
-  <si>
-    <t>'051</t>
-  </si>
-  <si>
-    <t>'0511</t>
-  </si>
-  <si>
-    <t>'0512</t>
-  </si>
-  <si>
-    <t>'052</t>
-  </si>
-  <si>
-    <t>'0520</t>
-  </si>
-  <si>
-    <t>'053</t>
-  </si>
-  <si>
-    <t>'0531</t>
-  </si>
-  <si>
-    <t>'0532</t>
-  </si>
-  <si>
-    <t>'0533</t>
-  </si>
-  <si>
-    <t>'054</t>
-  </si>
-  <si>
-    <t>'0540</t>
-  </si>
-  <si>
-    <t>'055</t>
-  </si>
-  <si>
-    <t>'0552</t>
-  </si>
-  <si>
-    <t>'056</t>
-  </si>
-  <si>
-    <t>'0561</t>
-  </si>
-  <si>
-    <t>'0562</t>
-  </si>
-  <si>
-    <t>'061</t>
-  </si>
-  <si>
-    <t>'0611</t>
-  </si>
-  <si>
-    <t>'0612</t>
-  </si>
-  <si>
-    <t>'0613</t>
-  </si>
-  <si>
-    <t>'062</t>
-  </si>
-  <si>
-    <t>'0621</t>
-  </si>
-  <si>
-    <t>'0622</t>
-  </si>
-  <si>
-    <t>'0623</t>
-  </si>
-  <si>
-    <t>'063</t>
-  </si>
-  <si>
-    <t>'0630</t>
-  </si>
-  <si>
-    <t>'071</t>
-  </si>
-  <si>
-    <t>'0711</t>
-  </si>
-  <si>
-    <t>'0712</t>
-  </si>
-  <si>
-    <t>'0713</t>
-  </si>
-  <si>
-    <t>'072</t>
-  </si>
-  <si>
-    <t>'0721</t>
-  </si>
-  <si>
-    <t>'0722</t>
-  </si>
-  <si>
-    <t>'0723</t>
-  </si>
-  <si>
-    <t>'0724</t>
-  </si>
-  <si>
-    <t>'073</t>
-  </si>
-  <si>
-    <t>'0731</t>
-  </si>
-  <si>
-    <t>'0732</t>
-  </si>
-  <si>
-    <t>'0733</t>
-  </si>
-  <si>
-    <t>'081</t>
-  </si>
-  <si>
-    <t>'0810</t>
-  </si>
-  <si>
-    <t>'082</t>
-  </si>
-  <si>
-    <t>'0820</t>
-  </si>
-  <si>
-    <t>'083</t>
-  </si>
-  <si>
-    <t>'0830</t>
-  </si>
-  <si>
-    <t>'091</t>
-  </si>
-  <si>
-    <t>'0911</t>
-  </si>
-  <si>
-    <t>'0912</t>
-  </si>
-  <si>
-    <t>'0913</t>
-  </si>
-  <si>
-    <t>'0914</t>
-  </si>
-  <si>
-    <t>'0915</t>
-  </si>
-  <si>
-    <t>'092</t>
-  </si>
-  <si>
-    <t>'0922</t>
-  </si>
-  <si>
-    <t>'093</t>
-  </si>
-  <si>
-    <t>'0931</t>
-  </si>
-  <si>
-    <t>'0932</t>
-  </si>
-  <si>
-    <t>'0933</t>
-  </si>
-  <si>
-    <t>'094</t>
-  </si>
-  <si>
-    <t>'0941</t>
-  </si>
-  <si>
-    <t>'0942</t>
-  </si>
-  <si>
-    <t>'0943</t>
-  </si>
-  <si>
-    <t>'095</t>
-  </si>
-  <si>
-    <t>'0951</t>
-  </si>
-  <si>
-    <t>'0952</t>
-  </si>
-  <si>
-    <t>'0954</t>
-  </si>
-  <si>
-    <t>'096</t>
-  </si>
-  <si>
-    <t>'0960</t>
-  </si>
-  <si>
-    <t>'01030</t>
-  </si>
-  <si>
-    <t>'0104</t>
-  </si>
-  <si>
-    <t>'01040</t>
-  </si>
-  <si>
-    <t>'0105</t>
-  </si>
-  <si>
-    <t>'01050</t>
-  </si>
-  <si>
-    <t>'01111</t>
-  </si>
-  <si>
-    <t>'01112</t>
-  </si>
-  <si>
-    <t>'01212</t>
-  </si>
-  <si>
-    <t>'01213</t>
-  </si>
-  <si>
-    <t>'0123</t>
-  </si>
-  <si>
-    <t>'01231</t>
-  </si>
-  <si>
-    <t>'01232</t>
-  </si>
-  <si>
-    <t>'0125</t>
-  </si>
-  <si>
-    <t>'01254</t>
-  </si>
-  <si>
-    <t>'0126</t>
-  </si>
-  <si>
-    <t>'01261</t>
-  </si>
-  <si>
-    <t>'0127</t>
-  </si>
-  <si>
-    <t>'01270</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
@@ -1224,348 +705,6 @@
     <t>Général</t>
   </si>
   <si>
-    <t>Produits Alimentaires</t>
-  </si>
-  <si>
-    <t>Produits Non Alimentaires</t>
-  </si>
-  <si>
-    <t>Produits Alimentaires Et Boissons Non Alcoolisees</t>
-  </si>
-  <si>
-    <t>Produits Alimentaires</t>
-  </si>
-  <si>
-    <t>Pain Et Cereales</t>
-  </si>
-  <si>
-    <t>Poisson Et Fruits De Mer</t>
-  </si>
-  <si>
-    <t>Lait, Fromage Et Oeufs</t>
-  </si>
-  <si>
-    <t>Huiles Et Graisses</t>
-  </si>
-  <si>
-    <t>Sucre, Confiture, Miel, Chocolat Et Confeserie</t>
-  </si>
-  <si>
-    <t>Produits Alimentaires N.C.A.</t>
-  </si>
-  <si>
-    <t>Boissons Non Alcoolisees</t>
-  </si>
-  <si>
-    <t>Cafe, The Et Cacao</t>
-  </si>
-  <si>
-    <t>Eaux Minerales, Boissons Rafraichissantes, Jus De Fruits Et De Legumes (Nd)</t>
-  </si>
-  <si>
-    <t>Boissons Alcoolisees, Tabac Et Stupefiants</t>
-  </si>
-  <si>
-    <t>Boissons Alcoolisees</t>
-  </si>
-  <si>
-    <t>Vin Et Boissons Fermentees</t>
-  </si>
-  <si>
-    <t>Articles D'Habillement Et Chaussures</t>
-  </si>
-  <si>
-    <t>Articles D'Habillement</t>
-  </si>
-  <si>
-    <t>Tissus Pour Habillement</t>
-  </si>
-  <si>
-    <t>Autres Articles Et Accessoires D'Habillement</t>
-  </si>
-  <si>
-    <t>Nettoyage, Reparation Et Location D'Articles D'Habillement</t>
-  </si>
-  <si>
-    <t>Chaussures Diverses</t>
-  </si>
-  <si>
-    <t>Logement, Eau, Gaz, Electricite Et Autres Combustibles</t>
-  </si>
-  <si>
-    <t>Loyers Effectifs</t>
-  </si>
-  <si>
-    <t>Loyers Effectivement Payes Par Les Locataires</t>
-  </si>
-  <si>
-    <t>Entretien Et Reparation De Logement</t>
-  </si>
-  <si>
-    <t>Fournitures Pour Travaux D'Entretien Et De Reparation Des Logement</t>
-  </si>
-  <si>
-    <t>Services Concernant L'Entretien Et Les Reparations Du Logement</t>
-  </si>
-  <si>
-    <t>Alimentation En Eau Et Services Divers Lies Au Logement</t>
-  </si>
-  <si>
-    <t>Alimentation En Eau Et Assainissement</t>
-  </si>
-  <si>
-    <t>Collecte Des Ordures Ménagères</t>
-  </si>
-  <si>
-    <t>Services Divers Liés Au Logement N.C.A</t>
-  </si>
-  <si>
-    <t>Electricite, Gaz Et Autres Combustibles</t>
-  </si>
-  <si>
-    <t>Combustibles Solides</t>
-  </si>
-  <si>
-    <t>Meubles, Articles De Menage Et Entretien Courant Du Foyer</t>
-  </si>
-  <si>
-    <t>Meubles, Articles D'Ameublement, Tapis Et Autres Revetements</t>
-  </si>
-  <si>
-    <t>Meubles Et Articles D'Ameublement</t>
-  </si>
-  <si>
-    <t>Tapis Et Revetements De Sol Divers</t>
-  </si>
-  <si>
-    <t>Articles De Menage En Textiles</t>
-  </si>
-  <si>
-    <t>Appareils Menagers</t>
-  </si>
-  <si>
-    <t>Gros Appareils Menagers,Electriques Ou Non</t>
-  </si>
-  <si>
-    <t>Petits Appareils Electromenagers</t>
-  </si>
-  <si>
-    <t>Reparation D'Appareils Menagers</t>
-  </si>
-  <si>
-    <t>Verrerie, Vaisselle Et Ustensiles De Menage</t>
-  </si>
-  <si>
-    <t>Outillage Et Autre Materiel Pour La Maison Et Le Jardin</t>
-  </si>
-  <si>
-    <t>Petit Outillage Et Accessoires Divers</t>
-  </si>
-  <si>
-    <t>Biens Et Services Lies A L'Entretien Courant Du Foyer</t>
-  </si>
-  <si>
-    <t>Biens D'Equipement Menager Non Durables</t>
-  </si>
-  <si>
-    <t>Services Domestiques Et Services Menagers</t>
-  </si>
-  <si>
-    <t>- Produits, Appareils Et Matériels Médicaux</t>
-  </si>
-  <si>
-    <t>Produits Pharmaceutiques</t>
-  </si>
-  <si>
-    <t>Produits Medicaux Divers</t>
-  </si>
-  <si>
-    <t>Appareils Et Materiel Therapeutiques</t>
-  </si>
-  <si>
-    <t>Services Ambulatoires</t>
-  </si>
-  <si>
-    <t>Services Medicaux</t>
-  </si>
-  <si>
-    <t>Services Dentaires</t>
-  </si>
-  <si>
-    <t>Services Paramedicaux</t>
-  </si>
-  <si>
-    <t>Services Hospitaliers</t>
-  </si>
-  <si>
-    <t>Achat De Vehicules</t>
-  </si>
-  <si>
-    <t>Voitures Automobiles</t>
-  </si>
-  <si>
-    <t>Depenses D'Utilisation Des Vehicules</t>
-  </si>
-  <si>
-    <t>Pieces De Rechange Et Accessoires Pour Vehicules De Tourisme</t>
-  </si>
-  <si>
-    <t>Carburants Et Lubrifiants Pour Vehicules De Tourisme</t>
-  </si>
-  <si>
-    <t>Entretien Et Reparation De Vehicules Particuliers</t>
-  </si>
-  <si>
-    <t>Services Divers Lies Aux Vehicules Particuliers</t>
-  </si>
-  <si>
-    <t>Services De Transport</t>
-  </si>
-  <si>
-    <t>Transport Ferroviaire De Passagers</t>
-  </si>
-  <si>
-    <t>Transport Routier De Passagers</t>
-  </si>
-  <si>
-    <t>Transport Aerien De Passagers</t>
-  </si>
-  <si>
-    <t>Services Postaux</t>
-  </si>
-  <si>
-    <t>Materiel De Telephonie Et De Telecopie</t>
-  </si>
-  <si>
-    <t>Services De Telephonie Et De Telecopie</t>
-  </si>
-  <si>
-    <t>Loisirs Et Culture</t>
-  </si>
-  <si>
-    <t>Materiel Audiovisuel, Photographique Et De Traitement De L'Information</t>
-  </si>
-  <si>
-    <t>Materiel De Reception, D'Enregistrement Et De Reproduction Du Son Et De L'Image</t>
-  </si>
-  <si>
-    <t>Materiel Photographique Et Cinematographique Et Appareils Optiques</t>
-  </si>
-  <si>
-    <t>Materiel De Traitement De L'Information</t>
-  </si>
-  <si>
-    <t>Supports D'Enregistrement</t>
-  </si>
-  <si>
-    <t>Reparation De Materiel Audiovisuel, Photographique Et De Traitement De L'Information</t>
-  </si>
-  <si>
-    <t>Autres Biens Durables À Fonction Récréative Et Culturelle</t>
-  </si>
-  <si>
-    <t>Instruments De Musique Et Biens Durables Destinés Aux Loisirs D'Intérieur</t>
-  </si>
-  <si>
-    <t>Autres Articles Et Materiel De Loisirs, De Jardinage Et Anim</t>
-  </si>
-  <si>
-    <t>Jeux, Jouets Et Passe-Temps</t>
-  </si>
-  <si>
-    <t>Articles De Sport, Materiel De Camping Et Materiel Pour Activites De Peil Air</t>
-  </si>
-  <si>
-    <t>Produits Pour Jardins, Plantes Et Fleurs</t>
-  </si>
-  <si>
-    <t>Services Recreatifs Et Culturels</t>
-  </si>
-  <si>
-    <t>Services Rcreatifs Et Sportifs</t>
-  </si>
-  <si>
-    <t>Services Culturels</t>
-  </si>
-  <si>
-    <t>Jeux De Hasard</t>
-  </si>
-  <si>
-    <t>Journaux, Livres Et Articles De Papeterie</t>
-  </si>
-  <si>
-    <t>Journaux Et Publications Periodiques</t>
-  </si>
-  <si>
-    <t>Papeterie Et Materiel De Dessin</t>
-  </si>
-  <si>
-    <t>Forfaits Touristiques</t>
-  </si>
-  <si>
-    <t>Enseignement Preelementaire Et Primaire</t>
-  </si>
-  <si>
-    <t>Enseignement Secondaire</t>
-  </si>
-  <si>
-    <t>Enseignement Postsecondaire Non Superieur</t>
-  </si>
-  <si>
-    <t>Enseignement Superieur</t>
-  </si>
-  <si>
-    <t>Enseignement Non Defini Par Niveau</t>
-  </si>
-  <si>
-    <t>Restaurants Et Hotels</t>
-  </si>
-  <si>
-    <t>Services De Restauration</t>
-  </si>
-  <si>
-    <t>Restaurants, Cafes Et Etablissements Similaires</t>
-  </si>
-  <si>
-    <t>Services D'Hebergement</t>
-  </si>
-  <si>
-    <t>Biens Et Services Divers</t>
-  </si>
-  <si>
-    <t>Soins Corporels</t>
-  </si>
-  <si>
-    <t>Salons De Coiffure Et Instituts De Soins Et De Beaute</t>
-  </si>
-  <si>
-    <t>Appareils Electriques Pour Soins Corporels</t>
-  </si>
-  <si>
-    <t>Autres Appareils, Articles Et Produits Pour Soins Corporels</t>
-  </si>
-  <si>
-    <t>Effets Personnels N.C.A.</t>
-  </si>
-  <si>
-    <t>Articles De Bijouterie Et Horlogerie</t>
-  </si>
-  <si>
-    <t>Autres Effets Personnels</t>
-  </si>
-  <si>
-    <t>Assurance Transports</t>
-  </si>
-  <si>
-    <t>Services Financiers</t>
-  </si>
-  <si>
-    <t>Cout Des Services D'Intermediation Financier</t>
-  </si>
-  <si>
-    <t>Autres Services</t>
-  </si>
-  <si>
     <t>عام</t>
   </si>
   <si>
@@ -2406,26 +1545,548 @@
     <t>Santé</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>0311</t>
+  </si>
+  <si>
+    <t>0312</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>0313</t>
+  </si>
+  <si>
+    <t>0314</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>0321</t>
+  </si>
+  <si>
+    <t>0322</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>0411</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>0431</t>
+  </si>
+  <si>
+    <t>0432</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>0441</t>
+  </si>
+  <si>
+    <t>0442</t>
+  </si>
+  <si>
+    <t>0444</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>0451</t>
+  </si>
+  <si>
+    <t>0452</t>
+  </si>
+  <si>
+    <t>0454</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>0511</t>
+  </si>
+  <si>
+    <t>0512</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>0520</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>0531</t>
+  </si>
+  <si>
+    <t>0532</t>
+  </si>
+  <si>
+    <t>0533</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>0540</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>0552</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>0561</t>
+  </si>
+  <si>
+    <t>0562</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>0611</t>
+  </si>
+  <si>
+    <t>0612</t>
+  </si>
+  <si>
+    <t>0613</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>0621</t>
+  </si>
+  <si>
+    <t>0622</t>
+  </si>
+  <si>
+    <t>0623</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>0630</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>0711</t>
+  </si>
+  <si>
+    <t>0712</t>
+  </si>
+  <si>
+    <t>0713</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>0721</t>
+  </si>
+  <si>
+    <t>0722</t>
+  </si>
+  <si>
+    <t>0723</t>
+  </si>
+  <si>
+    <t>0724</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>0731</t>
+  </si>
+  <si>
+    <t>0732</t>
+  </si>
+  <si>
+    <t>0733</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>0810</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>0820</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>0830</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>0911</t>
+  </si>
+  <si>
+    <t>0912</t>
+  </si>
+  <si>
+    <t>0913</t>
+  </si>
+  <si>
+    <t>0914</t>
+  </si>
+  <si>
+    <t>0915</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>0922</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>0931</t>
+  </si>
+  <si>
+    <t>0932</t>
+  </si>
+  <si>
+    <t>0933</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>0941</t>
+  </si>
+  <si>
+    <t>0942</t>
+  </si>
+  <si>
+    <t>0943</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>0951</t>
+  </si>
+  <si>
+    <t>0952</t>
+  </si>
+  <si>
+    <t>0954</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>0960</t>
+  </si>
+  <si>
+    <t>01030</t>
+  </si>
+  <si>
+    <t>0104</t>
+  </si>
+  <si>
+    <t>01040</t>
+  </si>
+  <si>
+    <t>0105</t>
+  </si>
+  <si>
+    <t>01050</t>
+  </si>
+  <si>
+    <t>01111</t>
+  </si>
+  <si>
+    <t>01112</t>
+  </si>
+  <si>
+    <t>01213</t>
+  </si>
+  <si>
+    <t>0123</t>
+  </si>
+  <si>
+    <t>01231</t>
+  </si>
+  <si>
+    <t>01232</t>
+  </si>
+  <si>
+    <t>0125</t>
+  </si>
+  <si>
+    <t>01254</t>
+  </si>
+  <si>
+    <t>0126</t>
+  </si>
+  <si>
+    <t>01261</t>
+  </si>
+  <si>
+    <t>0127</t>
+  </si>
+  <si>
+    <t>01270</t>
+  </si>
+  <si>
+    <t>Produits alimentaires et boissons non alcoolisées</t>
+  </si>
+  <si>
+    <t>Légumes</t>
+  </si>
+  <si>
+    <t>Boissons non alcoolisées</t>
+  </si>
+  <si>
+    <t>Café, thé et cacao</t>
+  </si>
+  <si>
+    <t>Eaux minerales, boissons rafraichissantes, jus de fruits et de légumes (nd)</t>
+  </si>
+  <si>
+    <t>Boissons alcoolisées</t>
+  </si>
+  <si>
+    <t>Vin et boissons fermentées</t>
+  </si>
+  <si>
+    <t>Bière</t>
+  </si>
+  <si>
+    <t>Vêtements</t>
+  </si>
+  <si>
+    <t>Nettoyage, réparation et location d'articles d'habillement</t>
+  </si>
+  <si>
+    <t>Logement, eau, gaz, électricité et autres combustibles</t>
+  </si>
+  <si>
+    <t>Loyers effectivement payés par les locataires</t>
+  </si>
+  <si>
+    <t>Entretien et réparation de logement</t>
+  </si>
+  <si>
+    <t>Fournitures pour travaux d'entretien et de réparation des logements</t>
+  </si>
+  <si>
+    <t>Services concernant l'entretien et les réparations du logement</t>
+  </si>
+  <si>
+    <t>Alimentation en eau et services divers liés au logement</t>
+  </si>
+  <si>
+    <t>Electricité, gaz et autres combustibles</t>
+  </si>
+  <si>
+    <t>Electricité</t>
+  </si>
+  <si>
+    <t>Meubles, articles de ménage et entretien courant du foyer</t>
+  </si>
+  <si>
+    <t>Meubles, articles d'ameublement, tapis et autres revêtements</t>
+  </si>
+  <si>
+    <t>Tapis et revêtements de sol divers</t>
+  </si>
+  <si>
+    <t>Articles de ménage en textiles</t>
+  </si>
+  <si>
+    <t>Appareils ménagers</t>
+  </si>
+  <si>
+    <t>Verrerie, vaisselle et ustensiles de ménage</t>
+  </si>
+  <si>
+    <t>Services domestiques et services ménagers</t>
+  </si>
+  <si>
+    <t>Pièces de rechange et accessoires pour véhicules de tourisme</t>
+  </si>
+  <si>
+    <t>Carburants et lubrifiants pour véhicules de tourisme</t>
+  </si>
+  <si>
+    <t>Entretien et réparation de véhicules particuliers</t>
+  </si>
+  <si>
+    <t>Pain et céréales</t>
+  </si>
+  <si>
+    <t>Lait, fromage et œufs</t>
+  </si>
+  <si>
+    <t>Sucre, confiture, miel, chocolat et confiserie</t>
+  </si>
+  <si>
+    <t>Boissons alcoolisées, tabac et stupéfiants</t>
+  </si>
+  <si>
+    <t>Gros appareils ménagers, électriques ou non</t>
+  </si>
+  <si>
+    <t>Petits appareils électroménagers</t>
+  </si>
+  <si>
+    <t>Réparation d'appareils ménagers</t>
+  </si>
+  <si>
+    <t>Outillage et autre matériel pour la maison et le jardin</t>
+  </si>
+  <si>
+    <t>Biens et services lies à l'entretien courant du foyer</t>
+  </si>
+  <si>
+    <t>Biens d'équipement ménager non durables</t>
+  </si>
+  <si>
+    <t>Produits médicaux divers</t>
+  </si>
+  <si>
+    <t>Appareils et matériel thérapeutiques</t>
+  </si>
+  <si>
+    <t>Services médicaux</t>
+  </si>
+  <si>
+    <t>Services paramédicaux</t>
+  </si>
+  <si>
+    <t>Achat de véhicules</t>
+  </si>
+  <si>
+    <t>Dépenses d'utilisation des véhicules</t>
+  </si>
+  <si>
+    <t>Services divers lies aux véhicules particuliers</t>
+  </si>
+  <si>
+    <t>Transport aérien de passagers</t>
+  </si>
+  <si>
+    <t>Matériel de téléphonie et de télécopie</t>
+  </si>
+  <si>
+    <t>Services de téléphonie et de télécopie</t>
+  </si>
+  <si>
+    <t>Matériel de traitement de l'information</t>
+  </si>
+  <si>
+    <t>Autres articles et matériel de loisirs, de jardinage et animaux d'agrément</t>
+  </si>
+  <si>
+    <t>Services récréatifs et culturels</t>
+  </si>
+  <si>
+    <t>Services récréatifs et sportifs</t>
+  </si>
+  <si>
+    <t>Journaux et publications périodiques</t>
+  </si>
+  <si>
+    <t>Papeterie et matériel de dessin</t>
+  </si>
+  <si>
+    <t>Enseignement préélémentaire et primaire</t>
+  </si>
+  <si>
+    <t>Enseignement postsecondaire non supérieur</t>
+  </si>
+  <si>
+    <t>Enseignement supérieur</t>
+  </si>
+  <si>
+    <t>Enseignement non défini par niveau</t>
+  </si>
+  <si>
+    <t>Restaurants et hôtels</t>
+  </si>
+  <si>
+    <t>Restaurants, cafés et établissements similaires</t>
+  </si>
+  <si>
+    <t>Services d'hébergement</t>
+  </si>
+  <si>
+    <t>Salons de coiffure et instituts de soins et de beauté</t>
+  </si>
+  <si>
+    <t>Appareils électriques pour soins corporels</t>
+  </si>
+  <si>
+    <t>Cout des services d'intermédiation financier</t>
+  </si>
+  <si>
+    <t>Produits, appareils et matériels médicaux</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>prep_fr</t>
+  </si>
+  <si>
+    <t>du</t>
+  </si>
+  <si>
     <t>0220</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>1211</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2443,6 +2104,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="TimesNewRomanPSMT"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2480,7 +2148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2488,7 +2156,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2783,3069 +2452,3523 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" customWidth="1"/>
-    <col min="3" max="3" width="56.140625" customWidth="1"/>
-    <col min="4" max="4" width="73.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.28515625" customWidth="1"/>
+    <col min="2" max="3" width="56.140625" customWidth="1"/>
+    <col min="4" max="4" width="56.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="51.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>271</v>
+      <c r="E1" t="s">
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A2" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="27" thickBot="1">
-      <c r="A3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>517</v>
+      <c r="E3" t="s">
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A4" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>403</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A5" s="5" t="s">
-        <v>381</v>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="27" thickBot="1">
+      <c r="A5" t="s">
+        <v>207</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>404</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="27" thickBot="1">
-      <c r="A6" s="5" t="s">
-        <v>383</v>
+        <v>683</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="E5" t="s">
+        <v>618</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A6" t="s">
+        <v>209</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
+        <v>683</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>683</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="E7" t="s">
+        <v>646</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>683</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>683</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>685</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="E10" t="s">
+        <v>647</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>683</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>683</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>683</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="E13" t="s">
+        <v>619</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="27" thickBot="1">
+      <c r="A14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>683</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="E14" t="s">
+        <v>648</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>683</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>683</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="E16" t="s">
+        <v>620</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>685</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="E17" t="s">
+        <v>621</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>683</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="E18" t="s">
+        <v>622</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="27" thickBot="1">
+      <c r="A19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>683</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="E19" t="s">
+        <v>649</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>683</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="E20" t="s">
+        <v>623</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>683</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A22" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>683</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="E22" t="s">
+        <v>624</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A23" t="s">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>683</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="E23" t="s">
+        <v>625</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A24" t="s">
+        <v>515</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>683</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A25" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>683</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A26" t="s">
+        <v>492</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>683</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A27" t="s">
+        <v>512</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>683</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A28" t="s">
+        <v>513</v>
+      </c>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>683</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A29" t="s">
+        <v>514</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>683</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="E29" t="s">
+        <v>626</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A30" t="s">
+        <v>516</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>683</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="27" thickBot="1">
+      <c r="A31" t="s">
+        <v>517</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>683</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="E31" t="s">
+        <v>627</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A32" t="s">
+        <v>518</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>683</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A33" t="s">
+        <v>519</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>683</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A34" t="s">
+        <v>520</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>683</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A35" t="s">
+        <v>493</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>683</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="E35" t="s">
+        <v>628</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A36" t="s">
+        <v>521</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>683</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="27" thickBot="1">
+      <c r="A37" t="s">
+        <v>522</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>683</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="E37" t="s">
+        <v>629</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A38" t="s">
+        <v>523</v>
+      </c>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>683</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="E38" t="s">
+        <v>630</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="27" thickBot="1">
+      <c r="A39" t="s">
+        <v>524</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" t="s">
+        <v>683</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="E39" t="s">
+        <v>631</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="27" thickBot="1">
+      <c r="A40" t="s">
+        <v>525</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
+        <v>683</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="E40" t="s">
+        <v>632</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A41" t="s">
+        <v>526</v>
+      </c>
+      <c r="B41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" t="s">
+        <v>683</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="E41" t="s">
+        <v>633</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="27" thickBot="1">
+      <c r="A42" t="s">
+        <v>527</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>683</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A43" t="s">
+        <v>528</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>683</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="27" thickBot="1">
+      <c r="A44" t="s">
+        <v>529</v>
+      </c>
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" t="s">
+        <v>683</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" t="s">
+        <v>65</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="27" thickBot="1">
+      <c r="A45" t="s">
+        <v>530</v>
+      </c>
+      <c r="B45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" t="s">
+        <v>683</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="E45" t="s">
+        <v>634</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A46" t="s">
+        <v>531</v>
+      </c>
+      <c r="B46" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" t="s">
+        <v>683</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="E46" t="s">
+        <v>635</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A47" t="s">
+        <v>532</v>
+      </c>
+      <c r="B47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
+        <v>683</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A48" t="s">
+        <v>533</v>
+      </c>
+      <c r="B48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" t="s">
+        <v>683</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="27" thickBot="1">
+      <c r="A49" t="s">
+        <v>494</v>
+      </c>
+      <c r="B49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" t="s">
+        <v>683</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="E49" t="s">
+        <v>636</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="27" thickBot="1">
+      <c r="A50" t="s">
+        <v>534</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
+        <v>683</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="E50" t="s">
+        <v>637</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A51" t="s">
+        <v>535</v>
+      </c>
+      <c r="B51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" t="s">
+        <v>683</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="27" thickBot="1">
+      <c r="A52" t="s">
+        <v>536</v>
+      </c>
+      <c r="B52" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" t="s">
+        <v>683</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="E52" t="s">
+        <v>638</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A53" t="s">
+        <v>537</v>
+      </c>
+      <c r="B53" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" t="s">
+        <v>683</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="E53" t="s">
+        <v>639</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A54" t="s">
+        <v>538</v>
+      </c>
+      <c r="B54" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" t="s">
+        <v>683</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="E54" t="s">
+        <v>639</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A55" t="s">
+        <v>539</v>
+      </c>
+      <c r="B55" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" t="s">
+        <v>683</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="E55" t="s">
+        <v>640</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="27" thickBot="1">
+      <c r="A56" t="s">
+        <v>540</v>
+      </c>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" t="s">
+        <v>683</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="E56" t="s">
+        <v>650</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A57" t="s">
+        <v>541</v>
+      </c>
+      <c r="B57" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" t="s">
+        <v>683</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="E57" t="s">
+        <v>651</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A58" t="s">
+        <v>542</v>
+      </c>
+      <c r="B58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s">
+        <v>683</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E58" t="s">
+        <v>652</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="27" thickBot="1">
+      <c r="A59" t="s">
+        <v>543</v>
+      </c>
+      <c r="B59" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" t="s">
+        <v>683</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="E59" t="s">
+        <v>641</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="27" thickBot="1">
+      <c r="A60" t="s">
+        <v>544</v>
+      </c>
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" t="s">
+        <v>683</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="E60" t="s">
+        <v>641</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="27" thickBot="1">
+      <c r="A61" t="s">
+        <v>545</v>
+      </c>
+      <c r="B61" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" t="s">
+        <v>683</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="E61" t="s">
+        <v>653</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="27" thickBot="1">
+      <c r="A62" t="s">
+        <v>546</v>
+      </c>
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" t="s">
+        <v>683</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" t="s">
+        <v>85</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="27" thickBot="1">
+      <c r="A63" t="s">
+        <v>547</v>
+      </c>
+      <c r="B63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" t="s">
+        <v>683</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="E63" t="s">
+        <v>654</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A64" t="s">
+        <v>548</v>
+      </c>
+      <c r="B64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" t="s">
+        <v>683</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="E64" t="s">
+        <v>655</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="27" thickBot="1">
+      <c r="A65" t="s">
+        <v>549</v>
+      </c>
+      <c r="B65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" t="s">
+        <v>683</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="E65" t="s">
+        <v>642</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A66" t="s">
+        <v>495</v>
+      </c>
+      <c r="B66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" t="s">
+        <v>683</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="E66" t="s">
+        <v>507</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="27" thickBot="1">
+      <c r="A67" t="s">
+        <v>550</v>
+      </c>
+      <c r="B67" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" t="s">
+        <v>683</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="E67" t="s">
+        <v>682</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A68" t="s">
+        <v>551</v>
+      </c>
+      <c r="B68" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" t="s">
+        <v>683</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" t="s">
+        <v>92</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A69" t="s">
+        <v>552</v>
+      </c>
+      <c r="B69" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" t="s">
+        <v>683</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="E69" t="s">
+        <v>656</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A70" t="s">
+        <v>553</v>
+      </c>
+      <c r="B70" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70" t="s">
+        <v>683</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="E70" t="s">
+        <v>657</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A71" t="s">
+        <v>554</v>
+      </c>
+      <c r="B71" t="s">
+        <v>95</v>
+      </c>
+      <c r="C71" t="s">
+        <v>683</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E71" t="s">
+        <v>96</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A72" t="s">
+        <v>555</v>
+      </c>
+      <c r="B72" t="s">
+        <v>97</v>
+      </c>
+      <c r="C72" t="s">
+        <v>683</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="E72" t="s">
+        <v>658</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A73" t="s">
+        <v>556</v>
+      </c>
+      <c r="B73" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" t="s">
+        <v>683</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E73" t="s">
+        <v>99</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A74" t="s">
+        <v>557</v>
+      </c>
+      <c r="B74" t="s">
+        <v>100</v>
+      </c>
+      <c r="C74" t="s">
+        <v>683</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="E74" t="s">
+        <v>659</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A75" t="s">
+        <v>558</v>
+      </c>
+      <c r="B75" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75" t="s">
+        <v>683</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E75" t="s">
+        <v>102</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A76" t="s">
+        <v>559</v>
+      </c>
+      <c r="B76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" t="s">
+        <v>683</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E76" t="s">
+        <v>102</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A77" t="s">
+        <v>496</v>
+      </c>
+      <c r="B77" t="s">
+        <v>103</v>
+      </c>
+      <c r="C77" t="s">
+        <v>683</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E77" t="s">
+        <v>104</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A78" t="s">
+        <v>560</v>
+      </c>
+      <c r="B78" t="s">
+        <v>105</v>
+      </c>
+      <c r="C78" t="s">
+        <v>683</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="E78" t="s">
+        <v>660</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A79" t="s">
+        <v>561</v>
+      </c>
+      <c r="B79" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" t="s">
+        <v>683</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E79" t="s">
+        <v>107</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A80" t="s">
+        <v>562</v>
+      </c>
+      <c r="B80" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" t="s">
+        <v>683</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" t="s">
+        <v>109</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A81" t="s">
+        <v>563</v>
+      </c>
+      <c r="B81" t="s">
+        <v>110</v>
+      </c>
+      <c r="C81" t="s">
+        <v>683</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E81" t="s">
+        <v>111</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A82" t="s">
+        <v>564</v>
+      </c>
+      <c r="B82" t="s">
+        <v>112</v>
+      </c>
+      <c r="C82" t="s">
+        <v>683</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="E82" t="s">
+        <v>661</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="27" thickBot="1">
+      <c r="A83" t="s">
+        <v>565</v>
+      </c>
+      <c r="B83" t="s">
+        <v>113</v>
+      </c>
+      <c r="C83" t="s">
+        <v>683</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="E83" t="s">
+        <v>643</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="27" thickBot="1">
+      <c r="A84" t="s">
+        <v>566</v>
+      </c>
+      <c r="B84" t="s">
+        <v>114</v>
+      </c>
+      <c r="C84" t="s">
+        <v>683</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="E84" t="s">
+        <v>644</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="27" thickBot="1">
+      <c r="A85" t="s">
+        <v>567</v>
+      </c>
+      <c r="B85" t="s">
+        <v>115</v>
+      </c>
+      <c r="C85" t="s">
+        <v>683</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="E85" t="s">
+        <v>645</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="27" thickBot="1">
+      <c r="A86" t="s">
+        <v>568</v>
+      </c>
+      <c r="B86" t="s">
+        <v>116</v>
+      </c>
+      <c r="C86" t="s">
+        <v>683</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="E86" t="s">
+        <v>662</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A87" t="s">
+        <v>569</v>
+      </c>
+      <c r="B87" t="s">
+        <v>117</v>
+      </c>
+      <c r="C87" t="s">
+        <v>683</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E87" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A88" t="s">
+        <v>570</v>
+      </c>
+      <c r="B88" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" t="s">
+        <v>683</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E88" t="s">
+        <v>120</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A89" t="s">
+        <v>571</v>
+      </c>
+      <c r="B89" t="s">
+        <v>121</v>
+      </c>
+      <c r="C89" t="s">
+        <v>683</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E89" t="s">
+        <v>122</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A90" t="s">
+        <v>572</v>
+      </c>
+      <c r="B90" t="s">
+        <v>123</v>
+      </c>
+      <c r="C90" t="s">
+        <v>683</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="E90" t="s">
+        <v>663</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A91" t="s">
+        <v>497</v>
+      </c>
+      <c r="B91" t="s">
+        <v>124</v>
+      </c>
+      <c r="C91" t="s">
+        <v>683</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E91" t="s">
+        <v>125</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A92" t="s">
+        <v>573</v>
+      </c>
+      <c r="B92" t="s">
+        <v>126</v>
+      </c>
+      <c r="C92" t="s">
+        <v>683</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E92" t="s">
+        <v>127</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A93" t="s">
+        <v>574</v>
+      </c>
+      <c r="B93" t="s">
+        <v>126</v>
+      </c>
+      <c r="C93" t="s">
+        <v>683</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E93" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A94" t="s">
+        <v>575</v>
+      </c>
+      <c r="B94" t="s">
+        <v>128</v>
+      </c>
+      <c r="C94" t="s">
+        <v>683</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="E94" t="s">
+        <v>664</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A95" t="s">
+        <v>576</v>
+      </c>
+      <c r="B95" t="s">
+        <v>128</v>
+      </c>
+      <c r="C95" t="s">
+        <v>683</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="E95" t="s">
+        <v>664</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A96" t="s">
+        <v>577</v>
+      </c>
+      <c r="B96" t="s">
+        <v>129</v>
+      </c>
+      <c r="C96" t="s">
+        <v>683</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="E96" t="s">
+        <v>665</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A97" t="s">
+        <v>578</v>
+      </c>
+      <c r="B97" t="s">
+        <v>129</v>
+      </c>
+      <c r="C97" t="s">
+        <v>683</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="E97" t="s">
+        <v>665</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A98" t="s">
+        <v>498</v>
+      </c>
+      <c r="B98" t="s">
+        <v>130</v>
+      </c>
+      <c r="C98" t="s">
+        <v>683</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E98" t="s">
+        <v>131</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A99" t="s">
+        <v>579</v>
+      </c>
+      <c r="B99" t="s">
+        <v>132</v>
+      </c>
+      <c r="C99" t="s">
+        <v>683</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E99" t="s">
+        <v>133</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="27" thickBot="1">
+      <c r="A100" t="s">
+        <v>580</v>
+      </c>
+      <c r="B100" t="s">
+        <v>134</v>
+      </c>
+      <c r="C100" t="s">
+        <v>683</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E100" t="s">
+        <v>135</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="27" thickBot="1">
+      <c r="A101" t="s">
+        <v>581</v>
+      </c>
+      <c r="B101" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" t="s">
+        <v>683</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E101" t="s">
+        <v>137</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A7" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="102" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A102" t="s">
+        <v>582</v>
+      </c>
+      <c r="B102" t="s">
+        <v>138</v>
+      </c>
+      <c r="C102" t="s">
+        <v>683</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="E102" t="s">
+        <v>666</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A8" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A9" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="G102" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A10" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="103" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A103" t="s">
+        <v>583</v>
+      </c>
+      <c r="B103" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103" t="s">
+        <v>683</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E103" t="s">
+        <v>140</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="27" thickBot="1">
-      <c r="A11" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="G103" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A12" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A13" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A14" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
+    </row>
+    <row r="104" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A104" t="s">
+        <v>584</v>
+      </c>
+      <c r="B104" t="s">
+        <v>141</v>
+      </c>
+      <c r="C104" t="s">
+        <v>683</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E104" t="s">
+        <v>142</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A15" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="G104" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A16" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s">
+    </row>
+    <row r="105" spans="1:7" ht="27" thickBot="1">
+      <c r="A105" t="s">
+        <v>585</v>
+      </c>
+      <c r="B105" t="s">
+        <v>143</v>
+      </c>
+      <c r="C105" t="s">
+        <v>683</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E105" t="s">
+        <v>143</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="G105" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="27" thickBot="1">
-      <c r="A18" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
+    </row>
+    <row r="106" spans="1:7" ht="27" thickBot="1">
+      <c r="A106" t="s">
+        <v>586</v>
+      </c>
+      <c r="B106" t="s">
+        <v>144</v>
+      </c>
+      <c r="C106" t="s">
+        <v>683</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E106" t="s">
+        <v>144</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="G106" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" t="s">
+    </row>
+    <row r="107" spans="1:7" ht="27" thickBot="1">
+      <c r="A107" t="s">
+        <v>587</v>
+      </c>
+      <c r="B107" t="s">
+        <v>145</v>
+      </c>
+      <c r="C107" t="s">
+        <v>683</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="E107" t="s">
+        <v>667</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="G107" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="4" t="s">
-        <v>796</v>
-      </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="B26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" t="s">
+    </row>
+    <row r="108" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A108" t="s">
+        <v>588</v>
+      </c>
+      <c r="B108" t="s">
+        <v>146</v>
+      </c>
+      <c r="C108" t="s">
+        <v>683</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" t="s">
+        <v>147</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="27" thickBot="1">
-      <c r="A27" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="G108" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="27" thickBot="1">
-      <c r="A28" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" t="s">
+    </row>
+    <row r="109" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A109" t="s">
+        <v>589</v>
+      </c>
+      <c r="B109" t="s">
+        <v>148</v>
+      </c>
+      <c r="C109" t="s">
+        <v>683</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E109" t="s">
+        <v>149</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="G109" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" t="s">
+    </row>
+    <row r="110" spans="1:7" ht="27" thickBot="1">
+      <c r="A110" t="s">
+        <v>590</v>
+      </c>
+      <c r="B110" t="s">
+        <v>150</v>
+      </c>
+      <c r="C110" t="s">
+        <v>683</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E110" t="s">
+        <v>151</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="27" thickBot="1">
-      <c r="A33" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B33" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="G110" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="27" thickBot="1">
-      <c r="A35" s="4" t="s">
-        <v>781</v>
-      </c>
-      <c r="B35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" t="s">
+    </row>
+    <row r="111" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A111" t="s">
+        <v>591</v>
+      </c>
+      <c r="B111" t="s">
+        <v>152</v>
+      </c>
+      <c r="C111" t="s">
+        <v>683</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="E111" t="s">
+        <v>668</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="27" thickBot="1">
-      <c r="A36" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="G111" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" t="s">
+    </row>
+    <row r="112" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A112" t="s">
+        <v>592</v>
+      </c>
+      <c r="B112" t="s">
+        <v>153</v>
+      </c>
+      <c r="C112" t="s">
+        <v>683</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E112" t="s">
+        <v>669</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="G112" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B39" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" t="s">
+    </row>
+    <row r="113" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A113" t="s">
+        <v>593</v>
+      </c>
+      <c r="B113" t="s">
+        <v>154</v>
+      </c>
+      <c r="C113" t="s">
+        <v>683</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E113" t="s">
+        <v>155</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="G113" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" t="s">
+    </row>
+    <row r="114" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A114" t="s">
+        <v>594</v>
+      </c>
+      <c r="B114" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114" t="s">
+        <v>683</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E114" t="s">
+        <v>157</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="G114" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" t="s">
+    </row>
+    <row r="115" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A115" t="s">
+        <v>595</v>
+      </c>
+      <c r="B115" t="s">
+        <v>158</v>
+      </c>
+      <c r="C115" t="s">
+        <v>683</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E115" t="s">
+        <v>159</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="G115" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" t="s">
-        <v>87</v>
-      </c>
-      <c r="D45" t="s">
+    </row>
+    <row r="116" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A116" t="s">
+        <v>596</v>
+      </c>
+      <c r="B116" t="s">
+        <v>160</v>
+      </c>
+      <c r="C116" t="s">
+        <v>683</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E116" t="s">
+        <v>161</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46" t="s">
-        <v>89</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>91</v>
-      </c>
-      <c r="D47" t="s">
-        <v>91</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="G116" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A117" t="s">
         <v>597</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="B117" t="s">
+        <v>162</v>
+      </c>
+      <c r="C117" t="s">
+        <v>683</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="E117" t="s">
+        <v>670</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A118" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B48" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" t="s">
-        <v>93</v>
-      </c>
-      <c r="D48" t="s">
-        <v>435</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="B118" t="s">
+        <v>163</v>
+      </c>
+      <c r="C118" t="s">
+        <v>683</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="E118" t="s">
+        <v>671</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A119" t="s">
         <v>599</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="B119" t="s">
+        <v>164</v>
+      </c>
+      <c r="C119" t="s">
+        <v>683</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E119" t="s">
+        <v>165</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A120" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="4" t="s">
-        <v>782</v>
-      </c>
-      <c r="B49" t="s">
-        <v>94</v>
-      </c>
-      <c r="C49" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" t="s">
-        <v>436</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="B120" t="s">
+        <v>164</v>
+      </c>
+      <c r="C120" t="s">
+        <v>683</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E120" t="s">
+        <v>165</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A121" t="s">
+        <v>499</v>
+      </c>
+      <c r="B121" t="s">
+        <v>166</v>
+      </c>
+      <c r="C121" t="s">
+        <v>683</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E121" t="s">
+        <v>167</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="27" thickBot="1">
+      <c r="A122" t="s">
+        <v>500</v>
+      </c>
+      <c r="B122" t="s">
+        <v>168</v>
+      </c>
+      <c r="C122" t="s">
+        <v>683</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="E122" t="s">
+        <v>672</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="27" thickBot="1">
+      <c r="A123" t="s">
+        <v>501</v>
+      </c>
+      <c r="B123" t="s">
+        <v>168</v>
+      </c>
+      <c r="C123" t="s">
+        <v>683</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="E123" t="s">
+        <v>672</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A124" t="s">
+        <v>502</v>
+      </c>
+      <c r="B124" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" t="s">
+        <v>683</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E124" t="s">
+        <v>170</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A125" t="s">
+        <v>503</v>
+      </c>
+      <c r="B125" t="s">
+        <v>169</v>
+      </c>
+      <c r="C125" t="s">
+        <v>683</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E125" t="s">
+        <v>170</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="27" thickBot="1">
+      <c r="A126" t="s">
+        <v>504</v>
+      </c>
+      <c r="B126" t="s">
+        <v>171</v>
+      </c>
+      <c r="C126" t="s">
+        <v>683</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="E126" t="s">
+        <v>673</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="27" thickBot="1">
+      <c r="A127" t="s">
         <v>601</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="B127" t="s">
+        <v>171</v>
+      </c>
+      <c r="C127" t="s">
+        <v>683</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="E127" t="s">
+        <v>673</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A128" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B50" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" t="s">
-        <v>437</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="B128" t="s">
+        <v>172</v>
+      </c>
+      <c r="C128" t="s">
+        <v>683</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E128" t="s">
+        <v>674</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A129" t="s">
         <v>603</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="B129" t="s">
+        <v>172</v>
+      </c>
+      <c r="C129" t="s">
+        <v>683</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E129" t="s">
+        <v>674</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A130" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" t="s">
-        <v>438</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="B130" t="s">
+        <v>173</v>
+      </c>
+      <c r="C130" t="s">
+        <v>683</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="E130" t="s">
+        <v>675</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A131" t="s">
         <v>605</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="B131" t="s">
+        <v>173</v>
+      </c>
+      <c r="C131" t="s">
+        <v>683</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="E131" t="s">
+        <v>675</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A132" t="s">
+        <v>505</v>
+      </c>
+      <c r="B132" t="s">
+        <v>174</v>
+      </c>
+      <c r="C132" t="s">
+        <v>683</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="E132" t="s">
+        <v>676</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A133" t="s">
+        <v>210</v>
+      </c>
+      <c r="B133" t="s">
+        <v>175</v>
+      </c>
+      <c r="C133" t="s">
+        <v>683</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E133" t="s">
+        <v>176</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="27" thickBot="1">
+      <c r="A134" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B52" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" t="s">
-        <v>439</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="B134" t="s">
+        <v>177</v>
+      </c>
+      <c r="C134" t="s">
+        <v>683</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="E134" t="s">
+        <v>677</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A135" t="s">
         <v>607</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="B135" t="s">
+        <v>178</v>
+      </c>
+      <c r="C135" t="s">
+        <v>683</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E135" t="s">
+        <v>179</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A136" t="s">
+        <v>508</v>
+      </c>
+      <c r="B136" t="s">
+        <v>180</v>
+      </c>
+      <c r="C136" t="s">
+        <v>683</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="E136" t="s">
+        <v>678</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A137" t="s">
+        <v>509</v>
+      </c>
+      <c r="B137" t="s">
+        <v>180</v>
+      </c>
+      <c r="C137" t="s">
+        <v>683</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="E137" t="s">
+        <v>678</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A138" t="s">
+        <v>506</v>
+      </c>
+      <c r="B138" t="s">
+        <v>181</v>
+      </c>
+      <c r="C138" t="s">
+        <v>683</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E138" t="s">
+        <v>182</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A139" t="s">
+        <v>510</v>
+      </c>
+      <c r="B139" t="s">
+        <v>183</v>
+      </c>
+      <c r="C139" t="s">
+        <v>683</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E139" t="s">
+        <v>184</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="27" thickBot="1">
+      <c r="A140" t="s">
+        <v>511</v>
+      </c>
+      <c r="B140" t="s">
+        <v>185</v>
+      </c>
+      <c r="C140" t="s">
+        <v>683</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="E140" t="s">
+        <v>679</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="27" thickBot="1">
+      <c r="A141">
+        <v>1212</v>
+      </c>
+      <c r="B141" t="s">
+        <v>186</v>
+      </c>
+      <c r="C141" t="s">
+        <v>683</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="E141" t="s">
+        <v>680</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="27" thickBot="1">
+      <c r="A142" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B53" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" t="s">
-        <v>440</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="B142" t="s">
+        <v>187</v>
+      </c>
+      <c r="C142" t="s">
+        <v>683</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E142" t="s">
+        <v>188</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A143" t="s">
         <v>609</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="B143" t="s">
+        <v>189</v>
+      </c>
+      <c r="C143" t="s">
+        <v>683</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E143" t="s">
+        <v>190</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="27" thickBot="1">
+      <c r="A144" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B54" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" t="s">
-        <v>440</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B55" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" t="s">
-        <v>441</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="B144" t="s">
+        <v>191</v>
+      </c>
+      <c r="C144" t="s">
+        <v>683</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E144" t="s">
+        <v>192</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A145" t="s">
         <v>611</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="B145" t="s">
+        <v>193</v>
+      </c>
+      <c r="C145" t="s">
+        <v>683</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E145" t="s">
+        <v>194</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A146" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="D56" t="s">
-        <v>442</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="B146" t="s">
+        <v>195</v>
+      </c>
+      <c r="C146" t="s">
+        <v>683</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E146" t="s">
+        <v>196</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A147" t="s">
         <v>613</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="B147" t="s">
+        <v>197</v>
+      </c>
+      <c r="C147" t="s">
+        <v>683</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E147" t="s">
+        <v>198</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A148" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B57" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" t="s">
-        <v>443</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="B148" t="s">
+        <v>199</v>
+      </c>
+      <c r="C148" t="s">
+        <v>683</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E148" t="s">
+        <v>200</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A149" t="s">
         <v>615</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="B149" t="s">
+        <v>201</v>
+      </c>
+      <c r="C149" t="s">
+        <v>683</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="E149" t="s">
+        <v>681</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A150" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B58" t="s">
-        <v>110</v>
-      </c>
-      <c r="C58" t="s">
-        <v>111</v>
-      </c>
-      <c r="D58" t="s">
-        <v>444</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="B150" t="s">
+        <v>202</v>
+      </c>
+      <c r="C150" t="s">
+        <v>683</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E150" t="s">
+        <v>203</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A151" t="s">
         <v>617</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B59" t="s">
-        <v>112</v>
-      </c>
-      <c r="C59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D59" t="s">
-        <v>445</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B60" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" t="s">
-        <v>113</v>
-      </c>
-      <c r="D60" t="s">
-        <v>445</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B61" t="s">
-        <v>114</v>
-      </c>
-      <c r="C61" t="s">
-        <v>115</v>
-      </c>
-      <c r="D61" t="s">
-        <v>446</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B62" t="s">
-        <v>116</v>
-      </c>
-      <c r="C62" t="s">
-        <v>117</v>
-      </c>
-      <c r="D62" t="s">
-        <v>447</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B63" t="s">
-        <v>118</v>
-      </c>
-      <c r="C63" t="s">
-        <v>119</v>
-      </c>
-      <c r="D63" t="s">
-        <v>448</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B64" t="s">
-        <v>120</v>
-      </c>
-      <c r="C64" t="s">
-        <v>121</v>
-      </c>
-      <c r="D64" t="s">
-        <v>449</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A65" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B65" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" t="s">
-        <v>123</v>
-      </c>
-      <c r="D65" t="s">
-        <v>450</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A66" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="B66" t="s">
-        <v>124</v>
-      </c>
-      <c r="C66" t="s">
-        <v>125</v>
-      </c>
-      <c r="D66" t="s">
-        <v>795</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A67" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B67" t="s">
-        <v>126</v>
-      </c>
-      <c r="C67" t="s">
-        <v>127</v>
-      </c>
-      <c r="D67" t="s">
-        <v>451</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A68" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B68" t="s">
-        <v>128</v>
-      </c>
-      <c r="C68" t="s">
-        <v>129</v>
-      </c>
-      <c r="D68" t="s">
-        <v>452</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A69" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B69" t="s">
-        <v>130</v>
-      </c>
-      <c r="C69" t="s">
-        <v>131</v>
-      </c>
-      <c r="D69" t="s">
-        <v>453</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A70" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B70" t="s">
-        <v>132</v>
-      </c>
-      <c r="C70" t="s">
-        <v>133</v>
-      </c>
-      <c r="D70" t="s">
-        <v>454</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A71" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B71" t="s">
-        <v>134</v>
-      </c>
-      <c r="C71" t="s">
-        <v>135</v>
-      </c>
-      <c r="D71" t="s">
-        <v>455</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A72" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B72" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" t="s">
-        <v>137</v>
-      </c>
-      <c r="D72" t="s">
-        <v>456</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="27" thickBot="1">
-      <c r="A73" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B73" t="s">
-        <v>138</v>
-      </c>
-      <c r="C73" t="s">
-        <v>139</v>
-      </c>
-      <c r="D73" t="s">
-        <v>457</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A74" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C74" t="s">
-        <v>141</v>
-      </c>
-      <c r="D74" t="s">
-        <v>458</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A75" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B75" t="s">
-        <v>142</v>
-      </c>
-      <c r="C75" t="s">
-        <v>143</v>
-      </c>
-      <c r="D75" t="s">
-        <v>459</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A76" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B76" t="s">
-        <v>142</v>
-      </c>
-      <c r="C76" t="s">
-        <v>143</v>
-      </c>
-      <c r="D76" t="s">
-        <v>459</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="27" thickBot="1">
-      <c r="A77" s="4" t="s">
-        <v>784</v>
-      </c>
-      <c r="B77" t="s">
-        <v>144</v>
-      </c>
-      <c r="C77" t="s">
-        <v>145</v>
-      </c>
-      <c r="D77" t="s">
-        <v>145</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A78" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" t="s">
-        <v>147</v>
-      </c>
-      <c r="D78" t="s">
-        <v>460</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A79" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B79" t="s">
-        <v>148</v>
-      </c>
-      <c r="C79" t="s">
-        <v>149</v>
-      </c>
-      <c r="D79" t="s">
-        <v>461</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A80" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B80" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D80" t="s">
-        <v>151</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A81" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B81" t="s">
-        <v>152</v>
-      </c>
-      <c r="C81" t="s">
-        <v>153</v>
-      </c>
-      <c r="D81" t="s">
-        <v>153</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A82" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B82" t="s">
-        <v>154</v>
-      </c>
-      <c r="C82" t="s">
-        <v>155</v>
-      </c>
-      <c r="D82" t="s">
-        <v>462</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A83" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B83" t="s">
-        <v>156</v>
-      </c>
-      <c r="C83" t="s">
-        <v>157</v>
-      </c>
-      <c r="D83" t="s">
-        <v>463</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A84" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B84" t="s">
-        <v>158</v>
-      </c>
-      <c r="C84" t="s">
-        <v>159</v>
-      </c>
-      <c r="D84" t="s">
-        <v>464</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A85" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B85" t="s">
-        <v>160</v>
-      </c>
-      <c r="C85" t="s">
-        <v>161</v>
-      </c>
-      <c r="D85" t="s">
-        <v>465</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A86" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B86" t="s">
-        <v>162</v>
-      </c>
-      <c r="C86" t="s">
-        <v>163</v>
-      </c>
-      <c r="D86" t="s">
-        <v>466</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A87" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B87" t="s">
-        <v>164</v>
-      </c>
-      <c r="C87" t="s">
-        <v>165</v>
-      </c>
-      <c r="D87" t="s">
-        <v>467</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A88" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B88" t="s">
-        <v>166</v>
-      </c>
-      <c r="C88" t="s">
-        <v>167</v>
-      </c>
-      <c r="D88" t="s">
-        <v>468</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A89" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B89" t="s">
-        <v>168</v>
-      </c>
-      <c r="C89" t="s">
-        <v>169</v>
-      </c>
-      <c r="D89" t="s">
-        <v>469</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A90" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B90" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" t="s">
-        <v>171</v>
-      </c>
-      <c r="D90" t="s">
-        <v>470</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A91" s="4" t="s">
-        <v>785</v>
-      </c>
-      <c r="B91" t="s">
-        <v>172</v>
-      </c>
-      <c r="C91" t="s">
-        <v>173</v>
-      </c>
-      <c r="D91" t="s">
-        <v>173</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="27" thickBot="1">
-      <c r="A92" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B92" t="s">
-        <v>174</v>
-      </c>
-      <c r="C92" t="s">
-        <v>175</v>
-      </c>
-      <c r="D92" t="s">
-        <v>471</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="27" thickBot="1">
-      <c r="A93" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B93" t="s">
-        <v>174</v>
-      </c>
-      <c r="C93" t="s">
-        <v>175</v>
-      </c>
-      <c r="D93" t="s">
-        <v>471</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A94" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B94" t="s">
-        <v>176</v>
-      </c>
-      <c r="C94" t="s">
-        <v>177</v>
-      </c>
-      <c r="D94" t="s">
-        <v>472</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A95" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B95" t="s">
-        <v>176</v>
-      </c>
-      <c r="C95" t="s">
-        <v>177</v>
-      </c>
-      <c r="D95" t="s">
-        <v>472</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A96" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B96" t="s">
-        <v>178</v>
-      </c>
-      <c r="C96" t="s">
-        <v>179</v>
-      </c>
-      <c r="D96" t="s">
-        <v>473</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A97" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B97" t="s">
-        <v>178</v>
-      </c>
-      <c r="C97" t="s">
-        <v>179</v>
-      </c>
-      <c r="D97" t="s">
-        <v>473</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A98" s="4" t="s">
-        <v>786</v>
-      </c>
-      <c r="B98" t="s">
-        <v>180</v>
-      </c>
-      <c r="C98" t="s">
-        <v>181</v>
-      </c>
-      <c r="D98" t="s">
-        <v>474</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="27" thickBot="1">
-      <c r="A99" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B99" t="s">
-        <v>182</v>
-      </c>
-      <c r="C99" t="s">
-        <v>183</v>
-      </c>
-      <c r="D99" t="s">
-        <v>475</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A100" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B100" t="s">
-        <v>184</v>
-      </c>
-      <c r="C100" t="s">
-        <v>185</v>
-      </c>
-      <c r="D100" t="s">
-        <v>476</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="27" thickBot="1">
-      <c r="A101" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B101" t="s">
-        <v>186</v>
-      </c>
-      <c r="C101" t="s">
-        <v>187</v>
-      </c>
-      <c r="D101" t="s">
-        <v>477</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A102" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B102" t="s">
-        <v>188</v>
-      </c>
-      <c r="C102" t="s">
-        <v>189</v>
-      </c>
-      <c r="D102" t="s">
-        <v>478</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A103" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B103" t="s">
-        <v>190</v>
-      </c>
-      <c r="C103" t="s">
-        <v>191</v>
-      </c>
-      <c r="D103" t="s">
-        <v>479</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="27" thickBot="1">
-      <c r="A104" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B104" t="s">
-        <v>192</v>
-      </c>
-      <c r="C104" t="s">
-        <v>193</v>
-      </c>
-      <c r="D104" t="s">
-        <v>480</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A105" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="B105" t="s">
-        <v>194</v>
-      </c>
-      <c r="C105" t="s">
-        <v>194</v>
-      </c>
-      <c r="D105" t="s">
-        <v>481</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A106" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="B106" t="s">
-        <v>195</v>
-      </c>
-      <c r="C106" t="s">
-        <v>195</v>
-      </c>
-      <c r="D106" t="s">
-        <v>482</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A107" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B107" t="s">
-        <v>196</v>
-      </c>
-      <c r="C107" t="s">
-        <v>197</v>
-      </c>
-      <c r="D107" t="s">
-        <v>483</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A108" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B108" t="s">
-        <v>198</v>
-      </c>
-      <c r="C108" t="s">
-        <v>199</v>
-      </c>
-      <c r="D108" t="s">
-        <v>484</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="27" thickBot="1">
-      <c r="A109" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B109" t="s">
-        <v>200</v>
-      </c>
-      <c r="C109" t="s">
-        <v>201</v>
-      </c>
-      <c r="D109" t="s">
-        <v>485</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A110" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B110" t="s">
+      <c r="B151" t="s">
         <v>202</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C151" t="s">
+        <v>683</v>
+      </c>
+      <c r="D151" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D110" t="s">
-        <v>486</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A111" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="B111" t="s">
-        <v>204</v>
-      </c>
-      <c r="C111" t="s">
-        <v>205</v>
-      </c>
-      <c r="D111" t="s">
-        <v>487</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A112" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B112" t="s">
-        <v>206</v>
-      </c>
-      <c r="C112" t="s">
-        <v>207</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="E151" t="s">
+        <v>203</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A113" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="B113" t="s">
-        <v>208</v>
-      </c>
-      <c r="C113" t="s">
-        <v>209</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="G151" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A114" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B114" t="s">
-        <v>210</v>
-      </c>
-      <c r="C114" t="s">
-        <v>211</v>
-      </c>
-      <c r="D114" t="s">
-        <v>490</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A115" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="B115" t="s">
-        <v>212</v>
-      </c>
-      <c r="C115" t="s">
-        <v>213</v>
-      </c>
-      <c r="D115" t="s">
-        <v>491</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A116" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B116" t="s">
-        <v>214</v>
-      </c>
-      <c r="C116" t="s">
-        <v>215</v>
-      </c>
-      <c r="D116" t="s">
-        <v>215</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A117" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B117" t="s">
-        <v>216</v>
-      </c>
-      <c r="C117" t="s">
-        <v>217</v>
-      </c>
-      <c r="D117" t="s">
-        <v>492</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A118" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B118" t="s">
-        <v>218</v>
-      </c>
-      <c r="C118" t="s">
-        <v>219</v>
-      </c>
-      <c r="D118" t="s">
-        <v>493</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A119" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B119" t="s">
-        <v>220</v>
-      </c>
-      <c r="C119" t="s">
-        <v>221</v>
-      </c>
-      <c r="D119" t="s">
-        <v>494</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A120" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="B120" t="s">
-        <v>220</v>
-      </c>
-      <c r="C120" t="s">
-        <v>221</v>
-      </c>
-      <c r="D120" t="s">
-        <v>494</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A121" s="4" t="s">
-        <v>787</v>
-      </c>
-      <c r="B121" t="s">
-        <v>222</v>
-      </c>
-      <c r="C121" t="s">
-        <v>223</v>
-      </c>
-      <c r="D121" t="s">
-        <v>223</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A122" s="4" t="s">
-        <v>788</v>
-      </c>
-      <c r="B122" t="s">
-        <v>224</v>
-      </c>
-      <c r="C122" t="s">
-        <v>225</v>
-      </c>
-      <c r="D122" t="s">
-        <v>495</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A123" s="4" t="s">
-        <v>789</v>
-      </c>
-      <c r="B123" t="s">
-        <v>224</v>
-      </c>
-      <c r="C123" t="s">
-        <v>225</v>
-      </c>
-      <c r="D123" t="s">
-        <v>495</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A124" s="4" t="s">
-        <v>790</v>
-      </c>
-      <c r="B124" t="s">
-        <v>226</v>
-      </c>
-      <c r="C124" t="s">
-        <v>227</v>
-      </c>
-      <c r="D124" t="s">
-        <v>496</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A125" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="B125" t="s">
-        <v>226</v>
-      </c>
-      <c r="C125" t="s">
-        <v>227</v>
-      </c>
-      <c r="D125" t="s">
-        <v>496</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A126" s="4" t="s">
-        <v>792</v>
-      </c>
-      <c r="B126" t="s">
-        <v>228</v>
-      </c>
-      <c r="C126" t="s">
-        <v>229</v>
-      </c>
-      <c r="D126" t="s">
-        <v>497</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A127" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B127" t="s">
-        <v>228</v>
-      </c>
-      <c r="C127" t="s">
-        <v>229</v>
-      </c>
-      <c r="D127" t="s">
-        <v>497</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A128" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="B128" t="s">
-        <v>230</v>
-      </c>
-      <c r="C128" t="s">
-        <v>231</v>
-      </c>
-      <c r="D128" t="s">
-        <v>498</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A129" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="B129" t="s">
-        <v>230</v>
-      </c>
-      <c r="C129" t="s">
-        <v>231</v>
-      </c>
-      <c r="D129" t="s">
-        <v>498</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A130" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="B130" t="s">
-        <v>232</v>
-      </c>
-      <c r="C130" t="s">
-        <v>233</v>
-      </c>
-      <c r="D130" t="s">
-        <v>499</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A131" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B131" t="s">
-        <v>232</v>
-      </c>
-      <c r="C131" t="s">
-        <v>233</v>
-      </c>
-      <c r="D131" t="s">
-        <v>499</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A132" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="B132" t="s">
-        <v>234</v>
-      </c>
-      <c r="C132" t="s">
-        <v>235</v>
-      </c>
-      <c r="D132" t="s">
-        <v>500</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A133" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B133" t="s">
-        <v>236</v>
-      </c>
-      <c r="C133" t="s">
-        <v>237</v>
-      </c>
-      <c r="D133" t="s">
-        <v>501</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A134" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B134" t="s">
-        <v>238</v>
-      </c>
-      <c r="C134" t="s">
-        <v>239</v>
-      </c>
-      <c r="D134" t="s">
-        <v>502</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A135" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="B135" t="s">
-        <v>240</v>
-      </c>
-      <c r="C135" t="s">
-        <v>241</v>
-      </c>
-      <c r="D135" t="s">
-        <v>241</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A136" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="B136" t="s">
-        <v>242</v>
-      </c>
-      <c r="C136" t="s">
-        <v>243</v>
-      </c>
-      <c r="D136" t="s">
-        <v>503</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A137" s="4" t="s">
-        <v>798</v>
-      </c>
-      <c r="B137" t="s">
-        <v>242</v>
-      </c>
-      <c r="C137" t="s">
-        <v>243</v>
-      </c>
-      <c r="D137" t="s">
-        <v>503</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A138" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="B138" t="s">
-        <v>244</v>
-      </c>
-      <c r="C138" t="s">
-        <v>245</v>
-      </c>
-      <c r="D138" t="s">
-        <v>504</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A139" s="4" t="s">
-        <v>799</v>
-      </c>
-      <c r="B139" t="s">
-        <v>246</v>
-      </c>
-      <c r="C139" t="s">
-        <v>247</v>
-      </c>
-      <c r="D139" t="s">
-        <v>505</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A140" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="B140" t="s">
-        <v>248</v>
-      </c>
-      <c r="C140" t="s">
-        <v>249</v>
-      </c>
-      <c r="D140" t="s">
-        <v>506</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A141" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="B141" t="s">
-        <v>250</v>
-      </c>
-      <c r="C141" t="s">
-        <v>251</v>
-      </c>
-      <c r="D141" t="s">
-        <v>507</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A142" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B142" t="s">
-        <v>252</v>
-      </c>
-      <c r="C142" t="s">
-        <v>253</v>
-      </c>
-      <c r="D142" t="s">
-        <v>508</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A143" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B143" t="s">
-        <v>254</v>
-      </c>
-      <c r="C143" t="s">
-        <v>255</v>
-      </c>
-      <c r="D143" t="s">
-        <v>509</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A144" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B144" t="s">
-        <v>256</v>
-      </c>
-      <c r="C144" t="s">
-        <v>257</v>
-      </c>
-      <c r="D144" t="s">
-        <v>510</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A145" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B145" t="s">
-        <v>258</v>
-      </c>
-      <c r="C145" t="s">
-        <v>259</v>
-      </c>
-      <c r="D145" t="s">
-        <v>511</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A146" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B146" t="s">
-        <v>260</v>
-      </c>
-      <c r="C146" t="s">
-        <v>261</v>
-      </c>
-      <c r="D146" t="s">
-        <v>261</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A147" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B147" t="s">
-        <v>262</v>
-      </c>
-      <c r="C147" t="s">
-        <v>263</v>
-      </c>
-      <c r="D147" t="s">
-        <v>512</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A148" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="B148" t="s">
-        <v>264</v>
-      </c>
-      <c r="C148" t="s">
-        <v>265</v>
-      </c>
-      <c r="D148" t="s">
-        <v>513</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A149" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B149" t="s">
-        <v>266</v>
-      </c>
-      <c r="C149" t="s">
-        <v>267</v>
-      </c>
-      <c r="D149" t="s">
-        <v>514</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="27" thickBot="1">
-      <c r="A150" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="B150" t="s">
-        <v>268</v>
-      </c>
-      <c r="C150" t="s">
-        <v>269</v>
-      </c>
-      <c r="D150" t="s">
-        <v>515</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="27" thickBot="1">
-      <c r="A151" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="B151" t="s">
-        <v>268</v>
-      </c>
-      <c r="C151" t="s">
-        <v>269</v>
-      </c>
-      <c r="D151" t="s">
-        <v>515</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="15.75" thickBot="1">
+    </row>
+    <row r="152" spans="1:7" ht="15.75" thickBot="1">
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="1:6" ht="15.75" thickBot="1">
+    <row r="153" spans="1:7" ht="15.75" thickBot="1">
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="1:6" ht="15.75" thickBot="1">
+    <row r="154" spans="1:7" ht="15.75" thickBot="1">
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="1:6" ht="15.75" thickBot="1">
+    <row r="155" spans="1:7" ht="15.75" thickBot="1">
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="1:6" ht="15.75" thickBot="1">
+    <row r="156" spans="1:7" ht="15.75" thickBot="1">
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="1:6" ht="15.75" thickBot="1">
+    <row r="157" spans="1:7" ht="15.75" thickBot="1">
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="1:6" ht="15.75" thickBot="1">
+    <row r="158" spans="1:7" ht="15.75" thickBot="1">
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
     </row>
-    <row r="159" spans="1:6" ht="15.75" thickBot="1">
+    <row r="159" spans="1:7" ht="15.75" thickBot="1">
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
     </row>
-    <row r="160" spans="1:6" ht="15.75" thickBot="1">
+    <row r="160" spans="1:7" ht="15.75" thickBot="1">
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
     </row>

--- a/Data_communes/lib_familles_produits.xlsx
+++ b/Data_communes/lib_familles_produits.xlsx
@@ -765,9 +765,6 @@
     <t>Sugar, Jam, Honey, Chocolate and Confectionery</t>
   </si>
   <si>
-    <t>Food Products N.C.A.</t>
-  </si>
-  <si>
     <t>المشروبات غير الكحولية</t>
   </si>
   <si>
@@ -915,9 +912,6 @@
     <t>خدمات إمدادات المياه وخدمات متنوعة متعلقة بالإسكان</t>
   </si>
   <si>
-    <t>Water Supply and Miscellaneous Housing-Related Services</t>
-  </si>
-  <si>
     <t>إمدادات المياه والصرف الصحي</t>
   </si>
   <si>
@@ -933,9 +927,6 @@
     <t>خدمات متنوعة متعلقة بالإسكان (NCA)</t>
   </si>
   <si>
-    <t>Miscellaneous Housing-Related Services N.C.A.</t>
-  </si>
-  <si>
     <t>الكهرباء والغاز وأنواع الوقود الأخرى</t>
   </si>
   <si>
@@ -1029,9 +1020,6 @@
     <t>أدوات صغيرة وملحقات متنوعة</t>
   </si>
   <si>
-    <t>Small Tools and Miscellaneous Accessories</t>
-  </si>
-  <si>
     <t>السلع والخدمات المتعلقة بالصيانة المنزلية الروتينية</t>
   </si>
   <si>
@@ -1071,9 +1059,6 @@
     <t>منتجات طبية متنوعة</t>
   </si>
   <si>
-    <t>Miscellaneous Medical Products</t>
-  </si>
-  <si>
     <t>الأجهزة والمعدات العلاجية</t>
   </si>
   <si>
@@ -1416,9 +1401,6 @@
     <t>سلع وخدمات متنوعة</t>
   </si>
   <si>
-    <t>Miscellaneous Goods and Services</t>
-  </si>
-  <si>
     <t>العناية بالجسم</t>
   </si>
   <si>
@@ -1443,12 +1425,6 @@
     <t>Other Devices, Items and Products for Personal Care</t>
   </si>
   <si>
-    <t>الأغراض الشخصية N.C.A.</t>
-  </si>
-  <si>
-    <t>Personal Effects N.C.A.</t>
-  </si>
-  <si>
     <t>أدوات صناعة المجوهرات والساعات</t>
   </si>
   <si>
@@ -2080,6 +2056,30 @@
   </si>
   <si>
     <t>0220</t>
+  </si>
+  <si>
+    <t>Food Productsnot elsewhere classified</t>
+  </si>
+  <si>
+    <t>الأغراض الشخصيةnot elsewhere classified</t>
+  </si>
+  <si>
+    <t>Personal Effectsnot elsewhere classified</t>
+  </si>
+  <si>
+    <t>Water Supply and Various Housing-Related Services</t>
+  </si>
+  <si>
+    <t>Various Housing-Related Servicesnot elsewhere classified</t>
+  </si>
+  <si>
+    <t>Small Tools and Various Accessories</t>
+  </si>
+  <si>
+    <t>Various Medical Products</t>
+  </si>
+  <si>
+    <t>Various Goods and Services</t>
   </si>
 </sst>
 </file>
@@ -2471,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -2494,7 +2494,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>227</v>
@@ -2517,7 +2517,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>8</v>
@@ -2540,7 +2540,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
@@ -2563,13 +2563,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="E5" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>233</v>
@@ -2586,7 +2586,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>8</v>
@@ -2609,13 +2609,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E7" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>235</v>
@@ -2632,7 +2632,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>15</v>
@@ -2641,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>237</v>
@@ -2655,7 +2655,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>17</v>
@@ -2678,13 +2678,13 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="E10" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>240</v>
@@ -2701,7 +2701,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>20</v>
@@ -2724,7 +2724,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>22</v>
@@ -2747,13 +2747,13 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="E13" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>244</v>
@@ -2770,13 +2770,13 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E14" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>246</v>
@@ -2793,7 +2793,7 @@
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>26</v>
@@ -2802,10 +2802,10 @@
         <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>248</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1">
@@ -2816,19 +2816,19 @@
         <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="E16" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
@@ -2839,19 +2839,19 @@
         <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="E17" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="39.75" thickBot="1">
@@ -2862,19 +2862,19 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="E18" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="27" thickBot="1">
@@ -2885,19 +2885,19 @@
         <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="E19" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" thickBot="1">
@@ -2908,19 +2908,19 @@
         <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E20" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" thickBot="1">
@@ -2931,7 +2931,7 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>33</v>
@@ -2940,10 +2940,10 @@
         <v>33</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" thickBot="1">
@@ -2954,19 +2954,19 @@
         <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="E22" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" thickBot="1">
@@ -2977,30 +2977,30 @@
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="E23" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" thickBot="1">
       <c r="A24" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B24" t="s">
         <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>37</v>
@@ -3009,21 +3009,21 @@
         <v>37</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" thickBot="1">
       <c r="A25" s="6" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>37</v>
@@ -3032,21 +3032,21 @@
         <v>37</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1">
       <c r="A26" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="B26" t="s">
         <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>39</v>
@@ -3055,21 +3055,21 @@
         <v>39</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" thickBot="1">
       <c r="A27" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B27" t="s">
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>41</v>
@@ -3078,21 +3078,21 @@
         <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" thickBot="1">
       <c r="A28" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B28" t="s">
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>43</v>
@@ -3101,44 +3101,44 @@
         <v>43</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" thickBot="1">
       <c r="A29" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="E29" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" thickBot="1">
       <c r="A30" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="B30" t="s">
         <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>46</v>
@@ -3147,44 +3147,44 @@
         <v>46</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="27" thickBot="1">
       <c r="A31" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="E31" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" thickBot="1">
       <c r="A32" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>49</v>
@@ -3193,21 +3193,21 @@
         <v>49</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" thickBot="1">
       <c r="A33" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>51</v>
@@ -3216,21 +3216,21 @@
         <v>51</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
       <c r="A34" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="B34" t="s">
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>53</v>
@@ -3239,44 +3239,44 @@
         <v>53</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="39.75" thickBot="1">
       <c r="A35" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="E35" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" thickBot="1">
       <c r="A36" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="B36" t="s">
         <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>56</v>
@@ -3285,136 +3285,136 @@
         <v>56</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="27" thickBot="1">
       <c r="A37" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B37" t="s">
         <v>57</v>
       </c>
       <c r="C37" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="E37" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
       <c r="A38" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B38" t="s">
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="E38" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="27" thickBot="1">
       <c r="A39" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B39" t="s">
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="E39" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="27" thickBot="1">
       <c r="A40" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B40" t="s">
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="E40" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="39.75" thickBot="1">
       <c r="A41" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="B41" t="s">
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E41" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>298</v>
+        <v>682</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="27" thickBot="1">
       <c r="A42" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>63</v>
@@ -3423,21 +3423,21 @@
         <v>63</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" thickBot="1">
       <c r="A43" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B43" t="s">
         <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>64</v>
@@ -3446,21 +3446,21 @@
         <v>64</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="27" thickBot="1">
       <c r="A44" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B44" t="s">
         <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>65</v>
@@ -3469,67 +3469,67 @@
         <v>65</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>304</v>
+        <v>683</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="27" thickBot="1">
       <c r="A45" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="B45" t="s">
         <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E45" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" thickBot="1">
       <c r="A46" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B46" t="s">
         <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E46" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" thickBot="1">
       <c r="A47" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B47" t="s">
         <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>69</v>
@@ -3538,21 +3538,21 @@
         <v>69</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" thickBot="1">
       <c r="A48" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B48" t="s">
         <v>70</v>
       </c>
       <c r="C48" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>71</v>
@@ -3561,67 +3561,67 @@
         <v>71</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="27" thickBot="1">
       <c r="A49" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B49" t="s">
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="E49" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="27" thickBot="1">
       <c r="A50" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B50" t="s">
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E50" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" thickBot="1">
       <c r="A51" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B51" t="s">
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>75</v>
@@ -3630,251 +3630,251 @@
         <v>75</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="27" thickBot="1">
       <c r="A52" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="B52" t="s">
         <v>76</v>
       </c>
       <c r="C52" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="E52" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" thickBot="1">
       <c r="A53" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="B53" t="s">
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E53" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" thickBot="1">
       <c r="A54" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="B54" t="s">
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E54" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" thickBot="1">
       <c r="A55" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="B55" t="s">
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="E55" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="27" thickBot="1">
       <c r="A56" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="B56" t="s">
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E56" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" thickBot="1">
       <c r="A57" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="B57" t="s">
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="E57" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.75" thickBot="1">
       <c r="A58" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B58" t="s">
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="E58" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="27" thickBot="1">
       <c r="A59" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="B59" t="s">
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="E59" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="27" thickBot="1">
       <c r="A60" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="B60" t="s">
         <v>82</v>
       </c>
       <c r="C60" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="E60" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="27" thickBot="1">
       <c r="A61" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B61" t="s">
         <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="E61" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="27" thickBot="1">
       <c r="A62" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B62" t="s">
         <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>85</v>
@@ -3883,136 +3883,136 @@
         <v>85</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>336</v>
+        <v>684</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="27" thickBot="1">
       <c r="A63" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B63" t="s">
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="E63" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" thickBot="1">
       <c r="A64" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s">
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="E64" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="27" thickBot="1">
       <c r="A65" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="B65" t="s">
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E65" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" thickBot="1">
       <c r="A66" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B66" t="s">
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="E66" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="27" thickBot="1">
       <c r="A67" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="B67" t="s">
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="E67" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" thickBot="1">
       <c r="A68" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B68" t="s">
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>92</v>
@@ -4021,67 +4021,67 @@
         <v>92</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" thickBot="1">
       <c r="A69" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="B69" t="s">
         <v>93</v>
       </c>
       <c r="C69" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="E69" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>350</v>
+        <v>685</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" thickBot="1">
       <c r="A70" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="B70" t="s">
         <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="E70" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" thickBot="1">
       <c r="A71" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="B71" t="s">
         <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>96</v>
@@ -4090,44 +4090,44 @@
         <v>96</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" thickBot="1">
       <c r="A72" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B72" t="s">
         <v>97</v>
       </c>
       <c r="C72" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="E72" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" thickBot="1">
       <c r="A73" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="B73" t="s">
         <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>99</v>
@@ -4136,44 +4136,44 @@
         <v>99</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" thickBot="1">
       <c r="A74" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s">
         <v>100</v>
       </c>
       <c r="C74" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="E74" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" thickBot="1">
       <c r="A75" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="B75" t="s">
         <v>101</v>
       </c>
       <c r="C75" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>102</v>
@@ -4182,21 +4182,21 @@
         <v>102</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.75" thickBot="1">
       <c r="A76" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B76" t="s">
         <v>101</v>
       </c>
       <c r="C76" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>102</v>
@@ -4205,21 +4205,21 @@
         <v>102</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.75" thickBot="1">
       <c r="A77" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B77" t="s">
         <v>103</v>
       </c>
       <c r="C77" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>104</v>
@@ -4228,44 +4228,44 @@
         <v>104</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.75" thickBot="1">
       <c r="A78" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="B78" t="s">
         <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E78" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" thickBot="1">
       <c r="A79" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B79" t="s">
         <v>106</v>
       </c>
       <c r="C79" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>107</v>
@@ -4274,21 +4274,21 @@
         <v>107</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15.75" thickBot="1">
       <c r="A80" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B80" t="s">
         <v>108</v>
       </c>
       <c r="C80" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>109</v>
@@ -4297,21 +4297,21 @@
         <v>109</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.75" thickBot="1">
       <c r="A81" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B81" t="s">
         <v>110</v>
       </c>
       <c r="C81" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>111</v>
@@ -4320,136 +4320,136 @@
         <v>111</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.75" thickBot="1">
       <c r="A82" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B82" t="s">
         <v>112</v>
       </c>
       <c r="C82" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="E82" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="27" thickBot="1">
       <c r="A83" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="B83" t="s">
         <v>113</v>
       </c>
       <c r="C83" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="E83" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="27" thickBot="1">
       <c r="A84" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="B84" t="s">
         <v>114</v>
       </c>
       <c r="C84" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="E84" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="27" thickBot="1">
       <c r="A85" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B85" t="s">
         <v>115</v>
       </c>
       <c r="C85" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="E85" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="27" thickBot="1">
       <c r="A86" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B86" t="s">
         <v>116</v>
       </c>
       <c r="C86" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="E86" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" thickBot="1">
       <c r="A87" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B87" t="s">
         <v>117</v>
       </c>
       <c r="C87" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>118</v>
@@ -4458,21 +4458,21 @@
         <v>118</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" thickBot="1">
       <c r="A88" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s">
         <v>119</v>
       </c>
       <c r="C88" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>120</v>
@@ -4481,21 +4481,21 @@
         <v>120</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" thickBot="1">
       <c r="A89" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B89" t="s">
         <v>121</v>
       </c>
       <c r="C89" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>122</v>
@@ -4504,44 +4504,44 @@
         <v>122</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" thickBot="1">
       <c r="A90" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="B90" t="s">
         <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="E90" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" thickBot="1">
       <c r="A91" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B91" t="s">
         <v>124</v>
       </c>
       <c r="C91" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>125</v>
@@ -4550,7 +4550,7 @@
         <v>125</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>125</v>
@@ -4558,13 +4558,13 @@
     </row>
     <row r="92" spans="1:7" ht="15.75" thickBot="1">
       <c r="A92" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="B92" t="s">
         <v>126</v>
       </c>
       <c r="C92" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>127</v>
@@ -4573,21 +4573,21 @@
         <v>127</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.75" thickBot="1">
       <c r="A93" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="B93" t="s">
         <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>127</v>
@@ -4596,113 +4596,113 @@
         <v>127</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" thickBot="1">
       <c r="A94" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="B94" t="s">
         <v>128</v>
       </c>
       <c r="C94" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="E94" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.75" thickBot="1">
       <c r="A95" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B95" t="s">
         <v>128</v>
       </c>
       <c r="C95" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="E95" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" thickBot="1">
       <c r="A96" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B96" t="s">
         <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E96" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15.75" thickBot="1">
       <c r="A97" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="B97" t="s">
         <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E97" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15.75" thickBot="1">
       <c r="A98" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B98" t="s">
         <v>130</v>
       </c>
       <c r="C98" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>131</v>
@@ -4711,21 +4711,21 @@
         <v>131</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="39.75" thickBot="1">
       <c r="A99" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B99" t="s">
         <v>132</v>
       </c>
       <c r="C99" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>133</v>
@@ -4734,21 +4734,21 @@
         <v>133</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="27" thickBot="1">
       <c r="A100" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B100" t="s">
         <v>134</v>
       </c>
       <c r="C100" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>135</v>
@@ -4757,21 +4757,21 @@
         <v>135</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="27" thickBot="1">
       <c r="A101" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B101" t="s">
         <v>136</v>
       </c>
       <c r="C101" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>137</v>
@@ -4780,44 +4780,44 @@
         <v>137</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15.75" thickBot="1">
       <c r="A102" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B102" t="s">
         <v>138</v>
       </c>
       <c r="C102" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="E102" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15.75" thickBot="1">
       <c r="A103" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="B103" t="s">
         <v>139</v>
       </c>
       <c r="C103" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>140</v>
@@ -4826,21 +4826,21 @@
         <v>140</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="39.75" thickBot="1">
       <c r="A104" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="B104" t="s">
         <v>141</v>
       </c>
       <c r="C104" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>142</v>
@@ -4849,21 +4849,21 @@
         <v>142</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="27" thickBot="1">
       <c r="A105" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B105" t="s">
         <v>143</v>
       </c>
       <c r="C105" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>143</v>
@@ -4872,21 +4872,21 @@
         <v>143</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="27" thickBot="1">
       <c r="A106" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B106" t="s">
         <v>144</v>
       </c>
       <c r="C106" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>144</v>
@@ -4895,44 +4895,44 @@
         <v>144</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="27" thickBot="1">
       <c r="A107" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B107" t="s">
         <v>145</v>
       </c>
       <c r="C107" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="E107" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15.75" thickBot="1">
       <c r="A108" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B108" t="s">
         <v>146</v>
       </c>
       <c r="C108" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>147</v>
@@ -4941,21 +4941,21 @@
         <v>147</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="39.75" thickBot="1">
       <c r="A109" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B109" t="s">
         <v>148</v>
       </c>
       <c r="C109" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>149</v>
@@ -4964,21 +4964,21 @@
         <v>149</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="27" thickBot="1">
       <c r="A110" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B110" t="s">
         <v>150</v>
       </c>
       <c r="C110" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>151</v>
@@ -4987,67 +4987,67 @@
         <v>151</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15.75" thickBot="1">
       <c r="A111" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="B111" t="s">
         <v>152</v>
       </c>
       <c r="C111" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="E111" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15.75" thickBot="1">
       <c r="A112" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B112" t="s">
         <v>153</v>
       </c>
       <c r="C112" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="E112" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15.75" thickBot="1">
       <c r="A113" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="B113" t="s">
         <v>154</v>
       </c>
       <c r="C113" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>155</v>
@@ -5056,21 +5056,21 @@
         <v>155</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15.75" thickBot="1">
       <c r="A114" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B114" t="s">
         <v>156</v>
       </c>
       <c r="C114" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>157</v>
@@ -5079,21 +5079,21 @@
         <v>157</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15.75" thickBot="1">
       <c r="A115" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B115" t="s">
         <v>158</v>
       </c>
       <c r="C115" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>159</v>
@@ -5102,21 +5102,21 @@
         <v>159</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15.75" thickBot="1">
       <c r="A116" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B116" t="s">
         <v>160</v>
       </c>
       <c r="C116" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>161</v>
@@ -5125,67 +5125,67 @@
         <v>161</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.75" thickBot="1">
       <c r="A117" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B117" t="s">
         <v>162</v>
       </c>
       <c r="C117" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="E117" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15.75" thickBot="1">
       <c r="A118" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B118" t="s">
         <v>163</v>
       </c>
       <c r="C118" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="E118" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15.75" thickBot="1">
       <c r="A119" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B119" t="s">
         <v>164</v>
       </c>
       <c r="C119" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>165</v>
@@ -5194,21 +5194,21 @@
         <v>165</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15.75" thickBot="1">
       <c r="A120" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B120" t="s">
         <v>164</v>
       </c>
       <c r="C120" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>165</v>
@@ -5217,21 +5217,21 @@
         <v>165</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15.75" thickBot="1">
       <c r="A121" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B121" t="s">
         <v>166</v>
       </c>
       <c r="C121" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>167</v>
@@ -5240,67 +5240,67 @@
         <v>167</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="27" thickBot="1">
       <c r="A122" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B122" t="s">
         <v>168</v>
       </c>
       <c r="C122" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="E122" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="27" thickBot="1">
       <c r="A123" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="B123" t="s">
         <v>168</v>
       </c>
       <c r="C123" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="E123" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15.75" thickBot="1">
       <c r="A124" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B124" t="s">
         <v>169</v>
       </c>
       <c r="C124" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>170</v>
@@ -5309,21 +5309,21 @@
         <v>170</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15.75" thickBot="1">
       <c r="A125" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B125" t="s">
         <v>169</v>
       </c>
       <c r="C125" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>170</v>
@@ -5332,171 +5332,171 @@
         <v>170</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="27" thickBot="1">
       <c r="A126" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="B126" t="s">
         <v>171</v>
       </c>
       <c r="C126" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="E126" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="27" thickBot="1">
       <c r="A127" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B127" t="s">
         <v>171</v>
       </c>
       <c r="C127" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="E127" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15.75" thickBot="1">
       <c r="A128" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B128" t="s">
         <v>172</v>
       </c>
       <c r="C128" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="E128" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15.75" thickBot="1">
       <c r="A129" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B129" t="s">
         <v>172</v>
       </c>
       <c r="C129" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="E129" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15.75" thickBot="1">
       <c r="A130" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="B130" t="s">
         <v>173</v>
       </c>
       <c r="C130" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="E130" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15.75" thickBot="1">
       <c r="A131" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B131" t="s">
         <v>173</v>
       </c>
       <c r="C131" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="E131" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15.75" thickBot="1">
       <c r="A132" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="B132" t="s">
         <v>174</v>
       </c>
       <c r="C132" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="E132" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15.75" thickBot="1">
@@ -5507,7 +5507,7 @@
         <v>175</v>
       </c>
       <c r="C133" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>176</v>
@@ -5516,44 +5516,44 @@
         <v>176</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="27" thickBot="1">
       <c r="A134" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B134" t="s">
         <v>177</v>
       </c>
       <c r="C134" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E134" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15.75" thickBot="1">
       <c r="A135" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B135" t="s">
         <v>178</v>
       </c>
       <c r="C135" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>179</v>
@@ -5562,67 +5562,67 @@
         <v>179</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15.75" thickBot="1">
       <c r="A136" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="B136" t="s">
         <v>180</v>
       </c>
       <c r="C136" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E136" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15.75" thickBot="1">
       <c r="A137" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B137" t="s">
         <v>180</v>
       </c>
       <c r="C137" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E137" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15.75" thickBot="1">
       <c r="A138" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B138" t="s">
         <v>181</v>
       </c>
       <c r="C138" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>182</v>
@@ -5631,21 +5631,21 @@
         <v>182</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>465</v>
+        <v>686</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15.75" thickBot="1">
       <c r="A139" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="B139" t="s">
         <v>183</v>
       </c>
       <c r="C139" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>184</v>
@@ -5654,33 +5654,33 @@
         <v>184</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="27" thickBot="1">
       <c r="A140" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B140" t="s">
         <v>185</v>
       </c>
       <c r="C140" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="E140" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="27" thickBot="1">
@@ -5691,30 +5691,30 @@
         <v>186</v>
       </c>
       <c r="C141" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="E141" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="27" thickBot="1">
       <c r="A142" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B142" t="s">
         <v>187</v>
       </c>
       <c r="C142" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>188</v>
@@ -5723,21 +5723,21 @@
         <v>188</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="15.75" thickBot="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="27" thickBot="1">
       <c r="A143" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B143" t="s">
         <v>189</v>
       </c>
       <c r="C143" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>190</v>
@@ -5746,21 +5746,21 @@
         <v>190</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>474</v>
+        <v>680</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>475</v>
+        <v>681</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="27" thickBot="1">
       <c r="A144" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B144" t="s">
         <v>191</v>
       </c>
       <c r="C144" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>192</v>
@@ -5769,21 +5769,21 @@
         <v>192</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15.75" thickBot="1">
       <c r="A145" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B145" t="s">
         <v>193</v>
       </c>
       <c r="C145" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>194</v>
@@ -5792,21 +5792,21 @@
         <v>194</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="15.75" thickBot="1">
       <c r="A146" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B146" t="s">
         <v>195</v>
       </c>
       <c r="C146" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>196</v>
@@ -5815,21 +5815,21 @@
         <v>196</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15.75" thickBot="1">
       <c r="A147" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s">
         <v>197</v>
       </c>
       <c r="C147" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>198</v>
@@ -5838,21 +5838,21 @@
         <v>198</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="15.75" thickBot="1">
       <c r="A148" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B148" t="s">
         <v>199</v>
       </c>
       <c r="C148" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>200</v>
@@ -5861,44 +5861,44 @@
         <v>200</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="15.75" thickBot="1">
       <c r="A149" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B149" t="s">
         <v>201</v>
       </c>
       <c r="C149" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="E149" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15.75" thickBot="1">
       <c r="A150" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="B150" t="s">
         <v>202</v>
       </c>
       <c r="C150" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>203</v>
@@ -5907,21 +5907,21 @@
         <v>203</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15.75" thickBot="1">
       <c r="A151" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B151" t="s">
         <v>202</v>
       </c>
       <c r="C151" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>203</v>
@@ -5930,10 +5930,10 @@
         <v>203</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="15.75" thickBot="1">
